--- a/B2B CAMPAÑAS.xlsx
+++ b/B2B CAMPAÑAS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EMANUEL.CONTRERAS\Desktop\B2B Y PRECISA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{458F7D00-B735-4295-9483-A671A64D02FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B61CECE0-54BD-40EE-AB9E-6B954044E4FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{7747799D-4BD1-4446-9F7D-9AFFD1051C34}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3710" uniqueCount="1017">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3821" uniqueCount="1017">
   <si>
     <t>DNI</t>
   </si>
@@ -3118,12 +3118,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3449,5660 +3447,5657 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" t="s">
         <v>173</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" t="s">
         <v>59</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="4">
+      <c r="A2" s="2">
         <v>46217</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" t="s">
         <v>175</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" t="s">
         <v>353</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" t="s">
         <v>624</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2" s="2">
         <v>30316</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2">
         <v>43</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" t="s">
         <v>946</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="3">
+      <c r="J2">
         <v>952227240</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="4">
+      <c r="A3" s="2">
         <v>46217</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" t="s">
         <v>175</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" t="s">
         <v>176</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" t="s">
         <v>354</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" t="s">
         <v>625</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="2">
         <v>39616</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3">
         <v>18</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" t="s">
         <v>30</v>
       </c>
-      <c r="I3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J3" s="3">
+      <c r="I3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J3">
         <v>931282962</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
+      <c r="A4" s="2">
         <v>46217</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" t="s">
         <v>175</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" t="s">
         <v>176</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" t="s">
         <v>355</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" t="s">
         <v>626</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="2">
         <v>38533</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4">
         <v>21</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" t="s">
         <v>162</v>
       </c>
-      <c r="I4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J4" s="3">
+      <c r="I4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J4">
         <v>935430407</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
+      <c r="A5" s="2">
         <v>46217</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" t="s">
         <v>175</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" t="s">
         <v>176</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5">
         <v>78552519</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" t="s">
         <v>627</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="2">
         <v>39633</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5">
         <v>18</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" t="s">
         <v>16</v>
       </c>
-      <c r="I5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J5" s="3">
+      <c r="I5" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5">
         <v>989265644</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
+      <c r="A6" s="2">
         <v>46217</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" t="s">
         <v>175</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" t="s">
         <v>176</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" t="s">
         <v>192</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" t="s">
         <v>193</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="2">
         <v>36732</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6">
         <v>26</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="H6" t="s">
         <v>92</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="I6" t="s">
         <v>17</v>
       </c>
-      <c r="J6" s="3">
+      <c r="J6">
         <v>979316486</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="4">
+      <c r="A7" s="2">
         <v>46217</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" t="s">
         <v>175</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" t="s">
         <v>176</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" t="s">
         <v>356</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" t="s">
         <v>628</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="2">
         <v>37734</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7">
         <v>23</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="H7" t="s">
         <v>102</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="I7" t="s">
         <v>17</v>
       </c>
-      <c r="J7" s="3">
+      <c r="J7">
         <v>918746516</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" s="4">
+      <c r="A8" s="2">
         <v>46217</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" t="s">
         <v>175</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" t="s">
         <v>176</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" t="s">
         <v>357</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" t="s">
         <v>629</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F8" s="2">
         <v>38434</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8">
         <v>21</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="H8" t="s">
         <v>45</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="I8" t="s">
         <v>17</v>
       </c>
-      <c r="J8" s="3">
+      <c r="J8">
         <v>943541173</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
+      <c r="A9" s="2">
         <v>46217</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" t="s">
         <v>175</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" t="s">
         <v>176</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" t="s">
         <v>358</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" t="s">
         <v>630</v>
       </c>
-      <c r="F9" s="4">
+      <c r="F9" s="2">
         <v>37980</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G9">
         <v>22</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="H9" t="s">
         <v>87</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J9" s="3">
+      <c r="I9" t="s">
+        <v>9</v>
+      </c>
+      <c r="J9">
         <v>908748110</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="4">
+      <c r="A10" s="2">
         <v>46217</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" t="s">
         <v>175</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" t="s">
         <v>176</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" t="s">
         <v>359</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" t="s">
         <v>631</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F10" s="2">
         <v>39349</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G10">
         <v>18</v>
       </c>
-      <c r="H10" s="3" t="s">
+      <c r="H10" t="s">
         <v>947</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="I10" t="s">
+        <v>9</v>
+      </c>
+      <c r="J10">
         <v>967854680</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="4">
+      <c r="A11" s="2">
         <v>46217</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" t="s">
         <v>175</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" t="s">
         <v>176</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" t="s">
         <v>360</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" t="s">
         <v>632</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="2">
         <v>29519</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G11">
         <v>45</v>
       </c>
-      <c r="H11" s="3" t="s">
+      <c r="H11" t="s">
         <v>102</v>
       </c>
-      <c r="I11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J11" s="3">
+      <c r="I11" t="s">
+        <v>9</v>
+      </c>
+      <c r="J11">
         <v>943923867</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="4">
+      <c r="A12" s="2">
         <v>46218</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" t="s">
         <v>175</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" t="s">
         <v>177</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" t="s">
         <v>361</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" t="s">
         <v>633</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F12" s="2">
         <v>28451</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12">
         <v>49</v>
       </c>
-      <c r="H12" s="3" t="s">
+      <c r="H12" t="s">
         <v>81</v>
       </c>
-      <c r="I12" s="3" t="s">
+      <c r="I12" t="s">
         <v>17</v>
       </c>
-      <c r="J12" s="3">
+      <c r="J12">
         <v>963930410</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="4">
+      <c r="A13" s="2">
         <v>46218</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" t="s">
         <v>175</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" t="s">
         <v>177</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" t="s">
         <v>198</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E13" t="s">
         <v>197</v>
       </c>
-      <c r="F13" s="4">
+      <c r="F13" s="2">
         <v>28523</v>
       </c>
-      <c r="G13" s="3">
+      <c r="G13">
         <v>48</v>
       </c>
-      <c r="H13" s="3" t="s">
+      <c r="H13" t="s">
         <v>38</v>
       </c>
-      <c r="I13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J13" s="3">
+      <c r="I13" t="s">
+        <v>9</v>
+      </c>
+      <c r="J13">
         <v>961326316</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="4">
+      <c r="A14" s="2">
         <v>46218</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" t="s">
         <v>175</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" t="s">
         <v>177</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" t="s">
         <v>362</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E14" t="s">
         <v>634</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F14" s="2">
         <v>34970</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14">
         <v>30</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="H14" t="s">
         <v>16</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="I14" t="s">
         <v>17</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14">
         <v>997277840</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="4">
+      <c r="A15" s="2">
         <v>46218</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" t="s">
         <v>175</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" t="s">
         <v>177</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" t="s">
         <v>194</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="E15" t="s">
         <v>195</v>
       </c>
-      <c r="F15" s="4">
+      <c r="F15" s="2">
         <v>22979</v>
       </c>
-      <c r="G15" s="3">
+      <c r="G15">
         <v>63</v>
       </c>
-      <c r="H15" s="3" t="s">
+      <c r="H15" t="s">
         <v>196</v>
       </c>
-      <c r="I15" s="3" t="s">
+      <c r="I15" t="s">
         <v>17</v>
       </c>
-      <c r="J15" s="3">
+      <c r="J15">
         <v>991279603</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="4">
+      <c r="A16" s="2">
         <v>46218</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" t="s">
         <v>175</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" t="s">
         <v>177</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" t="s">
         <v>363</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="E16" t="s">
         <v>635</v>
       </c>
-      <c r="F16" s="4">
+      <c r="F16" s="2">
         <v>38110</v>
       </c>
-      <c r="G16" s="3">
+      <c r="G16">
         <v>22</v>
       </c>
-      <c r="H16" s="3" t="s">
+      <c r="H16" t="s">
         <v>45</v>
       </c>
-      <c r="I16" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J16" s="3">
+      <c r="I16" t="s">
+        <v>9</v>
+      </c>
+      <c r="J16">
         <v>927729963</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
+      <c r="A17" s="2">
         <v>46218</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" t="s">
         <v>175</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" t="s">
         <v>177</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" t="s">
         <v>364</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="E17" t="s">
         <v>636</v>
       </c>
-      <c r="F17" s="4">
+      <c r="F17" s="2">
         <v>24564</v>
       </c>
-      <c r="G17" s="3">
+      <c r="G17">
         <v>59</v>
       </c>
-      <c r="H17" s="3" t="s">
+      <c r="H17" t="s">
         <v>45</v>
       </c>
-      <c r="I17" s="3" t="s">
+      <c r="I17" t="s">
         <v>17</v>
       </c>
-      <c r="J17" s="3">
+      <c r="J17">
         <v>967885403</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A18" s="4">
+      <c r="A18" s="2">
         <v>46218</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" t="s">
         <v>175</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" t="s">
         <v>177</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D18" t="s">
         <v>365</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="E18" t="s">
         <v>637</v>
       </c>
-      <c r="F18" s="4">
+      <c r="F18" s="2">
         <v>36696</v>
       </c>
-      <c r="G18" s="3">
+      <c r="G18">
         <v>26</v>
       </c>
-      <c r="H18" s="3" t="s">
+      <c r="H18" t="s">
         <v>45</v>
       </c>
-      <c r="I18" s="3" t="s">
+      <c r="I18" t="s">
         <v>17</v>
       </c>
-      <c r="J18" s="3">
+      <c r="J18">
         <v>933072528</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" s="4">
+      <c r="A19" s="2">
         <v>46218</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" t="s">
         <v>175</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" t="s">
         <v>177</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" t="s">
         <v>366</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="E19" t="s">
         <v>638</v>
       </c>
-      <c r="F19" s="4">
+      <c r="F19" s="2">
         <v>36328</v>
       </c>
-      <c r="G19" s="3">
+      <c r="G19">
         <v>27</v>
       </c>
-      <c r="H19" s="3" t="s">
+      <c r="H19" t="s">
         <v>16</v>
       </c>
-      <c r="I19" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J19" s="3">
+      <c r="I19" t="s">
+        <v>9</v>
+      </c>
+      <c r="J19">
         <v>986753496</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" s="4">
+      <c r="A20" s="2">
         <v>46218</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" t="s">
         <v>175</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" t="s">
         <v>177</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" t="s">
         <v>367</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="E20" t="s">
         <v>639</v>
       </c>
-      <c r="F20" s="4">
+      <c r="F20" s="2">
         <v>38118</v>
       </c>
-      <c r="G20" s="3">
+      <c r="G20">
         <v>22</v>
       </c>
-      <c r="H20" s="3" t="s">
+      <c r="H20" t="s">
         <v>45</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="I20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J20">
         <v>904823572</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A21" s="4">
+      <c r="A21" s="2">
         <v>46218</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" t="s">
         <v>175</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" t="s">
         <v>177</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="D21" t="s">
         <v>368</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="E21" t="s">
         <v>640</v>
       </c>
-      <c r="F21" s="4">
+      <c r="F21" s="2">
         <v>35871</v>
       </c>
-      <c r="G21" s="3">
+      <c r="G21">
         <v>28</v>
       </c>
-      <c r="H21" s="3" t="s">
+      <c r="H21" t="s">
         <v>16</v>
       </c>
-      <c r="I21" s="3" t="s">
+      <c r="I21" t="s">
         <v>17</v>
       </c>
-      <c r="J21" s="3">
+      <c r="J21">
         <v>938269428</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A22" s="4">
+      <c r="A22" s="2">
         <v>46218</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" t="s">
         <v>175</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" t="s">
         <v>177</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="D22" t="s">
         <v>205</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="E22" t="s">
         <v>204</v>
       </c>
-      <c r="F22" s="4">
+      <c r="F22" s="2">
         <v>33102</v>
       </c>
-      <c r="G22" s="3">
+      <c r="G22">
         <v>35</v>
       </c>
-      <c r="H22" s="3" t="s">
+      <c r="H22" t="s">
         <v>45</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J22" s="3">
+      <c r="I22" t="s">
+        <v>9</v>
+      </c>
+      <c r="J22">
         <v>987658080</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A23" s="4">
+      <c r="A23" s="2">
         <v>46218</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" t="s">
         <v>175</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" t="s">
         <v>177</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="D23" t="s">
         <v>369</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="E23" t="s">
         <v>641</v>
       </c>
-      <c r="F23" s="4">
+      <c r="F23" s="2">
         <v>37501</v>
       </c>
-      <c r="G23" s="3">
+      <c r="G23">
         <v>23</v>
       </c>
-      <c r="H23" s="3" t="s">
+      <c r="H23" t="s">
         <v>16</v>
       </c>
-      <c r="I23" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="I23" t="s">
+        <v>9</v>
+      </c>
+      <c r="J23">
         <v>969479077</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A24" s="4">
+      <c r="A24" s="2">
         <v>46218</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" t="s">
         <v>175</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" t="s">
         <v>177</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="D24" t="s">
         <v>370</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="E24" t="s">
         <v>642</v>
       </c>
-      <c r="F24" s="4">
+      <c r="F24" s="2">
         <v>37243</v>
       </c>
-      <c r="G24" s="3">
+      <c r="G24">
         <v>24</v>
       </c>
-      <c r="H24" s="3" t="s">
+      <c r="H24" t="s">
         <v>16</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J24" s="3">
+      <c r="I24" t="s">
+        <v>9</v>
+      </c>
+      <c r="J24">
         <v>916954842</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A25" s="4">
+      <c r="A25" s="2">
         <v>46218</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" t="s">
         <v>175</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" t="s">
         <v>177</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="D25" t="s">
         <v>371</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="E25" t="s">
         <v>643</v>
       </c>
-      <c r="F25" s="4">
+      <c r="F25" s="2">
         <v>34418</v>
       </c>
-      <c r="G25" s="3">
+      <c r="G25">
         <v>32</v>
       </c>
-      <c r="H25" s="3" t="s">
+      <c r="H25" t="s">
         <v>30</v>
       </c>
-      <c r="I25" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J25" s="3">
+      <c r="I25" t="s">
+        <v>9</v>
+      </c>
+      <c r="J25">
         <v>994029449</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A26" s="4">
+      <c r="A26" s="2">
         <v>46218</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" t="s">
         <v>175</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" t="s">
         <v>177</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="D26" t="s">
         <v>372</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="E26" t="s">
         <v>644</v>
       </c>
-      <c r="F26" s="4">
+      <c r="F26" s="2">
         <v>37068</v>
       </c>
-      <c r="G26" s="3">
+      <c r="G26">
         <v>25</v>
       </c>
-      <c r="H26" s="3" t="s">
+      <c r="H26" t="s">
         <v>30</v>
       </c>
-      <c r="I26" s="3" t="s">
+      <c r="I26" t="s">
         <v>17</v>
       </c>
-      <c r="J26" s="3">
+      <c r="J26">
         <v>953309756</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A27" s="4">
+      <c r="A27" s="2">
         <v>46218</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" t="s">
         <v>175</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C27" t="s">
         <v>177</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="D27" t="s">
         <v>201</v>
       </c>
-      <c r="E27" s="3" t="s">
+      <c r="E27" t="s">
         <v>200</v>
       </c>
-      <c r="F27" s="4">
+      <c r="F27" s="2">
         <v>37268</v>
       </c>
-      <c r="G27" s="3">
+      <c r="G27">
         <v>24</v>
       </c>
-      <c r="H27" s="3" t="s">
+      <c r="H27" t="s">
         <v>45</v>
       </c>
-      <c r="I27" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J27" s="3">
+      <c r="I27" t="s">
+        <v>9</v>
+      </c>
+      <c r="J27">
         <v>926909142</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A28" s="4">
+      <c r="A28" s="2">
         <v>46218</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" t="s">
         <v>175</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" t="s">
         <v>177</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="D28" t="s">
         <v>373</v>
       </c>
-      <c r="E28" s="3" t="s">
+      <c r="E28" t="s">
         <v>645</v>
       </c>
-      <c r="F28" s="4">
+      <c r="F28" s="2">
         <v>36564</v>
       </c>
-      <c r="G28" s="3">
+      <c r="G28">
         <v>26</v>
       </c>
-      <c r="H28" s="3" t="s">
+      <c r="H28" t="s">
         <v>45</v>
       </c>
-      <c r="I28" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J28" s="3">
+      <c r="I28" t="s">
+        <v>9</v>
+      </c>
+      <c r="J28">
         <v>979518014</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A29" s="4">
+      <c r="A29" s="2">
         <v>46218</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" t="s">
         <v>175</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C29" t="s">
         <v>177</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="D29" t="s">
         <v>374</v>
       </c>
-      <c r="E29" s="3" t="s">
+      <c r="E29" t="s">
         <v>199</v>
       </c>
-      <c r="F29" s="4">
+      <c r="F29" s="2">
         <v>34969</v>
       </c>
-      <c r="G29" s="3">
+      <c r="G29">
         <v>30</v>
       </c>
-      <c r="H29" s="3" t="s">
+      <c r="H29" t="s">
         <v>16</v>
       </c>
-      <c r="I29" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J29" s="3">
+      <c r="I29" t="s">
+        <v>9</v>
+      </c>
+      <c r="J29">
         <v>986198301</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A30" s="4">
+      <c r="A30" s="2">
         <v>46218</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" t="s">
         <v>175</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" t="s">
         <v>177</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="D30" t="s">
         <v>375</v>
       </c>
-      <c r="E30" s="3" t="s">
+      <c r="E30" t="s">
         <v>646</v>
       </c>
-      <c r="F30" s="4">
+      <c r="F30" s="2">
         <v>36806</v>
       </c>
-      <c r="G30" s="3">
+      <c r="G30">
         <v>25</v>
       </c>
-      <c r="H30" s="3" t="s">
+      <c r="H30" t="s">
         <v>45</v>
       </c>
-      <c r="I30" s="3" t="s">
+      <c r="I30" t="s">
         <v>17</v>
       </c>
-      <c r="J30" s="3">
+      <c r="J30">
         <v>951302357</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A31" s="4">
+      <c r="A31" s="2">
         <v>46218</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" t="s">
         <v>175</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C31" t="s">
         <v>177</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="D31" t="s">
         <v>203</v>
       </c>
-      <c r="E31" s="3" t="s">
+      <c r="E31" t="s">
         <v>202</v>
       </c>
-      <c r="F31" s="4">
+      <c r="F31" s="2">
         <v>34410</v>
       </c>
-      <c r="G31" s="3">
+      <c r="G31">
         <v>32</v>
       </c>
-      <c r="H31" s="3" t="s">
+      <c r="H31" t="s">
         <v>30</v>
       </c>
-      <c r="I31" s="3" t="s">
+      <c r="I31" t="s">
         <v>17</v>
       </c>
-      <c r="J31" s="3">
+      <c r="J31">
         <v>935286861</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A32" s="4">
+      <c r="A32" s="2">
         <v>46218</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" t="s">
         <v>175</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C32" t="s">
         <v>177</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="D32" t="s">
         <v>376</v>
       </c>
-      <c r="E32" s="3" t="s">
+      <c r="E32" t="s">
         <v>647</v>
       </c>
-      <c r="F32" s="4">
+      <c r="F32" s="2">
         <v>37749</v>
       </c>
-      <c r="G32" s="3">
+      <c r="G32">
         <v>23</v>
       </c>
-      <c r="H32" s="3" t="s">
+      <c r="H32" t="s">
         <v>948</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="I32" t="s">
+        <v>9</v>
+      </c>
+      <c r="J32">
         <v>935409657</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A33" s="4">
+      <c r="A33" s="2">
         <v>46218</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B33" t="s">
         <v>175</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C33" t="s">
         <v>177</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="D33" t="s">
         <v>377</v>
       </c>
-      <c r="E33" s="3" t="s">
+      <c r="E33" t="s">
         <v>648</v>
       </c>
-      <c r="F33" s="4">
+      <c r="F33" s="2">
         <v>35830</v>
       </c>
-      <c r="G33" s="3">
+      <c r="G33">
         <v>28</v>
       </c>
-      <c r="H33" s="3" t="s">
+      <c r="H33" t="s">
         <v>45</v>
       </c>
-      <c r="I33" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J33" s="3">
+      <c r="I33" t="s">
+        <v>9</v>
+      </c>
+      <c r="J33">
         <v>979744149</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A34" s="4">
+      <c r="A34" s="2">
         <v>46218</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B34" t="s">
         <v>175</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C34" t="s">
         <v>177</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="D34" t="s">
         <v>378</v>
       </c>
-      <c r="E34" s="3" t="s">
+      <c r="E34" t="s">
         <v>216</v>
       </c>
-      <c r="F34" s="4">
+      <c r="F34" s="2">
         <v>37332</v>
       </c>
-      <c r="G34" s="3">
+      <c r="G34">
         <v>24</v>
       </c>
-      <c r="H34" s="3" t="s">
+      <c r="H34" t="s">
         <v>287</v>
       </c>
-      <c r="I34" s="3" t="s">
+      <c r="I34" t="s">
         <v>17</v>
       </c>
-      <c r="J34" s="3">
+      <c r="J34">
         <v>977516919</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A35" s="4">
+      <c r="A35" s="2">
         <v>46218</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B35" t="s">
         <v>175</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C35" t="s">
         <v>177</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="D35" t="s">
         <v>379</v>
       </c>
-      <c r="E35" s="3" t="s">
+      <c r="E35" t="s">
         <v>649</v>
       </c>
-      <c r="F35" s="4">
+      <c r="F35" s="2">
         <v>32458</v>
       </c>
-      <c r="G35" s="3">
+      <c r="G35">
         <v>37</v>
       </c>
-      <c r="H35" s="3" t="s">
+      <c r="H35" t="s">
         <v>45</v>
       </c>
-      <c r="I35" s="3" t="s">
+      <c r="I35" t="s">
         <v>17</v>
       </c>
-      <c r="J35" s="3">
+      <c r="J35">
         <v>957321827</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A36" s="4">
+      <c r="A36" s="2">
         <v>46218</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B36" t="s">
         <v>175</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C36" t="s">
         <v>177</v>
       </c>
-      <c r="D36" s="3" t="s">
+      <c r="D36" t="s">
         <v>380</v>
       </c>
-      <c r="E36" s="3" t="s">
+      <c r="E36" t="s">
         <v>650</v>
       </c>
-      <c r="F36" s="4">
+      <c r="F36" s="2">
         <v>37664</v>
       </c>
-      <c r="G36" s="3">
+      <c r="G36">
         <v>23</v>
       </c>
-      <c r="H36" s="3" t="s">
+      <c r="H36" t="s">
         <v>16</v>
       </c>
-      <c r="I36" s="3" t="s">
+      <c r="I36" t="s">
         <v>17</v>
       </c>
-      <c r="J36" s="3">
+      <c r="J36">
         <v>925131522</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A37" s="4">
+      <c r="A37" s="2">
         <v>46218</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B37" t="s">
         <v>175</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="C37" t="s">
         <v>177</v>
       </c>
-      <c r="D37" s="3" t="s">
+      <c r="D37" t="s">
         <v>207</v>
       </c>
-      <c r="E37" s="3" t="s">
+      <c r="E37" t="s">
         <v>206</v>
       </c>
-      <c r="F37" s="4">
+      <c r="F37" s="2">
         <v>29746</v>
       </c>
-      <c r="G37" s="3">
+      <c r="G37">
         <v>45</v>
       </c>
-      <c r="H37" s="3" t="s">
+      <c r="H37" t="s">
         <v>16</v>
       </c>
-      <c r="I37" s="3" t="s">
+      <c r="I37" t="s">
         <v>17</v>
       </c>
-      <c r="J37" s="3">
+      <c r="J37">
         <v>910499184</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A38" s="4">
+      <c r="A38" s="2">
         <v>46218</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B38" t="s">
         <v>175</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C38" t="s">
         <v>177</v>
       </c>
-      <c r="D38" s="3" t="s">
+      <c r="D38" t="s">
         <v>381</v>
       </c>
-      <c r="E38" s="3" t="s">
+      <c r="E38" t="s">
         <v>651</v>
       </c>
-      <c r="F38" s="4">
+      <c r="F38" s="2">
         <v>37019</v>
       </c>
-      <c r="G38" s="3">
+      <c r="G38">
         <v>25</v>
       </c>
-      <c r="H38" s="3" t="s">
+      <c r="H38" t="s">
         <v>949</v>
       </c>
-      <c r="I38" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J38" s="3">
+      <c r="I38" t="s">
+        <v>9</v>
+      </c>
+      <c r="J38">
         <v>968280337</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A39" s="4">
+      <c r="A39" s="2">
         <v>46218</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B39" t="s">
         <v>175</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C39" t="s">
         <v>177</v>
       </c>
-      <c r="D39" s="3" t="s">
+      <c r="D39" t="s">
         <v>209</v>
       </c>
-      <c r="E39" s="3" t="s">
+      <c r="E39" t="s">
         <v>208</v>
       </c>
-      <c r="F39" s="4">
+      <c r="F39" s="2">
         <v>38786</v>
       </c>
-      <c r="G39" s="3">
+      <c r="G39">
         <v>20</v>
       </c>
-      <c r="H39" s="3" t="s">
+      <c r="H39" t="s">
         <v>45</v>
       </c>
-      <c r="I39" s="3" t="s">
+      <c r="I39" t="s">
         <v>17</v>
       </c>
-      <c r="J39" s="3">
+      <c r="J39">
         <v>921107191</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A40" s="4">
+      <c r="A40" s="2">
         <v>46218</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B40" t="s">
         <v>175</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="C40" t="s">
         <v>177</v>
       </c>
-      <c r="D40" s="3" t="s">
+      <c r="D40" t="s">
         <v>211</v>
       </c>
-      <c r="E40" s="3" t="s">
+      <c r="E40" t="s">
         <v>210</v>
       </c>
-      <c r="F40" s="4">
+      <c r="F40" s="2">
         <v>29928</v>
       </c>
-      <c r="G40" s="3">
+      <c r="G40">
         <v>44</v>
       </c>
-      <c r="H40" s="3" t="s">
+      <c r="H40" t="s">
         <v>45</v>
       </c>
-      <c r="I40" s="3" t="s">
+      <c r="I40" t="s">
         <v>17</v>
       </c>
-      <c r="J40" s="3">
+      <c r="J40">
         <v>974788116</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A41" s="4">
+      <c r="A41" s="2">
         <v>46218</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B41" t="s">
         <v>175</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="C41" t="s">
         <v>177</v>
       </c>
-      <c r="D41" s="3" t="s">
+      <c r="D41" t="s">
         <v>382</v>
       </c>
-      <c r="E41" s="3" t="s">
+      <c r="E41" t="s">
         <v>652</v>
       </c>
-      <c r="F41" s="4">
+      <c r="F41" s="2">
         <v>29825</v>
       </c>
-      <c r="G41" s="3">
+      <c r="G41">
         <v>44</v>
       </c>
-      <c r="H41" s="3" t="s">
+      <c r="H41" t="s">
         <v>950</v>
       </c>
-      <c r="I41" s="3" t="s">
+      <c r="I41" t="s">
         <v>17</v>
       </c>
-      <c r="J41" s="3">
+      <c r="J41">
         <v>944603116</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A42" s="4">
+      <c r="A42" s="2">
         <v>46219</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="B42" t="s">
         <v>175</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="C42" t="s">
         <v>177</v>
       </c>
-      <c r="D42" s="3" t="s">
+      <c r="D42" t="s">
         <v>383</v>
       </c>
-      <c r="E42" s="3" t="s">
+      <c r="E42" t="s">
         <v>653</v>
       </c>
-      <c r="F42" s="4">
+      <c r="F42" s="2">
         <v>28138</v>
       </c>
-      <c r="G42" s="3">
+      <c r="G42">
         <v>49</v>
       </c>
-      <c r="H42" s="3" t="s">
+      <c r="H42" t="s">
         <v>30</v>
       </c>
-      <c r="I42" s="3" t="s">
+      <c r="I42" t="s">
         <v>17</v>
       </c>
-      <c r="J42" s="3"/>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A43" s="4">
+      <c r="A43" s="2">
         <v>46219</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="B43" t="s">
         <v>175</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="C43" t="s">
         <v>177</v>
       </c>
-      <c r="D43" s="3" t="s">
+      <c r="D43" t="s">
         <v>384</v>
       </c>
-      <c r="E43" s="3" t="s">
+      <c r="E43" t="s">
         <v>212</v>
       </c>
-      <c r="F43" s="4">
+      <c r="F43" s="2">
         <v>32892</v>
       </c>
-      <c r="G43" s="3">
+      <c r="G43">
         <v>36</v>
       </c>
-      <c r="H43" s="3" t="s">
+      <c r="H43" t="s">
         <v>87</v>
       </c>
-      <c r="I43" s="3" t="s">
+      <c r="I43" t="s">
         <v>17</v>
       </c>
-      <c r="J43" s="3">
+      <c r="J43">
         <v>902623012</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A44" s="4">
+      <c r="A44" s="2">
         <v>46219</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="B44" t="s">
         <v>175</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="C44" t="s">
         <v>177</v>
       </c>
-      <c r="D44" s="3" t="s">
+      <c r="D44" t="s">
         <v>385</v>
       </c>
-      <c r="E44" s="3" t="s">
+      <c r="E44" t="s">
         <v>213</v>
       </c>
-      <c r="F44" s="4">
+      <c r="F44" s="2">
         <v>36316</v>
       </c>
-      <c r="G44" s="3">
+      <c r="G44">
         <v>27</v>
       </c>
-      <c r="H44" s="3" t="s">
+      <c r="H44" t="s">
         <v>16</v>
       </c>
-      <c r="I44" s="3" t="s">
+      <c r="I44" t="s">
         <v>17</v>
       </c>
-      <c r="J44" s="3">
+      <c r="J44">
         <v>961876449</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A45" s="4">
+      <c r="A45" s="2">
         <v>46219</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="B45" t="s">
         <v>175</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="C45" t="s">
         <v>177</v>
       </c>
-      <c r="D45" s="3" t="s">
+      <c r="D45" t="s">
         <v>386</v>
       </c>
-      <c r="E45" s="3" t="s">
+      <c r="E45" t="s">
         <v>654</v>
       </c>
-      <c r="F45" s="4">
+      <c r="F45" s="2">
         <v>35867</v>
       </c>
-      <c r="G45" s="3">
+      <c r="G45">
         <v>28</v>
       </c>
-      <c r="H45" s="3" t="s">
+      <c r="H45" t="s">
         <v>261</v>
       </c>
-      <c r="I45" s="3" t="s">
+      <c r="I45" t="s">
         <v>17</v>
       </c>
-      <c r="J45" s="3">
+      <c r="J45">
         <v>991047981</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A46" s="4">
+      <c r="A46" s="2">
         <v>46219</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="B46" t="s">
         <v>175</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="C46" t="s">
         <v>177</v>
       </c>
-      <c r="D46" s="3" t="s">
+      <c r="D46" t="s">
         <v>387</v>
       </c>
-      <c r="E46" s="3" t="s">
+      <c r="E46" t="s">
         <v>655</v>
       </c>
-      <c r="F46" s="4">
+      <c r="F46" s="2">
         <v>32955</v>
       </c>
-      <c r="G46" s="3">
+      <c r="G46">
         <v>36</v>
       </c>
-      <c r="H46" s="3" t="s">
+      <c r="H46" t="s">
         <v>16</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J46" s="3">
+      <c r="I46" t="s">
+        <v>9</v>
+      </c>
+      <c r="J46">
         <v>974462951</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A47" s="4">
+      <c r="A47" s="2">
         <v>46219</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="B47" t="s">
         <v>175</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="C47" t="s">
         <v>177</v>
       </c>
-      <c r="D47" s="3" t="s">
+      <c r="D47" t="s">
         <v>388</v>
       </c>
-      <c r="E47" s="3" t="s">
+      <c r="E47" t="s">
         <v>656</v>
       </c>
-      <c r="F47" s="4">
+      <c r="F47" s="2">
         <v>36933</v>
       </c>
-      <c r="G47" s="3">
+      <c r="G47">
         <v>25</v>
       </c>
-      <c r="H47" s="3" t="s">
+      <c r="H47" t="s">
         <v>16</v>
       </c>
-      <c r="I47" s="3" t="s">
+      <c r="I47" t="s">
         <v>17</v>
       </c>
-      <c r="J47" s="3">
+      <c r="J47">
         <v>960554958</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A48" s="4">
+      <c r="A48" s="2">
         <v>46219</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="B48" t="s">
         <v>175</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="C48" t="s">
         <v>177</v>
       </c>
-      <c r="D48" s="3" t="s">
+      <c r="D48" t="s">
         <v>389</v>
       </c>
-      <c r="E48" s="3" t="s">
+      <c r="E48" t="s">
         <v>657</v>
       </c>
-      <c r="F48" s="4">
+      <c r="F48" s="2">
         <v>38391</v>
       </c>
-      <c r="G48" s="3">
+      <c r="G48">
         <v>21</v>
       </c>
-      <c r="H48" s="3" t="s">
+      <c r="H48" t="s">
         <v>16</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J48" s="3">
+      <c r="I48" t="s">
+        <v>9</v>
+      </c>
+      <c r="J48">
         <v>972362560</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A49" s="4">
+      <c r="A49" s="2">
         <v>46219</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="B49" t="s">
         <v>175</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="C49" t="s">
         <v>177</v>
       </c>
-      <c r="D49" s="3" t="s">
+      <c r="D49" t="s">
         <v>215</v>
       </c>
-      <c r="E49" s="3" t="s">
+      <c r="E49" t="s">
         <v>214</v>
       </c>
-      <c r="F49" s="4">
+      <c r="F49" s="2">
         <v>33275</v>
       </c>
-      <c r="G49" s="3">
+      <c r="G49">
         <v>35</v>
       </c>
-      <c r="H49" s="3" t="s">
+      <c r="H49" t="s">
         <v>13</v>
       </c>
-      <c r="I49" s="3" t="s">
+      <c r="I49" t="s">
         <v>17</v>
       </c>
-      <c r="J49" s="3">
+      <c r="J49">
         <v>915077753</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A50" s="4">
+      <c r="A50" s="2">
         <v>46219</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="B50" t="s">
         <v>175</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="C50" t="s">
         <v>177</v>
       </c>
-      <c r="D50" s="3" t="s">
+      <c r="D50" t="s">
         <v>390</v>
       </c>
-      <c r="E50" s="3" t="s">
+      <c r="E50" t="s">
         <v>658</v>
       </c>
-      <c r="F50" s="4">
+      <c r="F50" s="2">
         <v>35908</v>
       </c>
-      <c r="G50" s="3">
+      <c r="G50">
         <v>28</v>
       </c>
-      <c r="H50" s="3" t="s">
+      <c r="H50" t="s">
         <v>949</v>
       </c>
-      <c r="I50" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J50" s="3">
+      <c r="I50" t="s">
+        <v>9</v>
+      </c>
+      <c r="J50">
         <v>978600168</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A51" s="4">
+      <c r="A51" s="2">
         <v>46220</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="B51" t="s">
         <v>175</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="C51" t="s">
         <v>178</v>
       </c>
-      <c r="D51" s="3" t="s">
+      <c r="D51" t="s">
         <v>391</v>
       </c>
-      <c r="E51" s="3" t="s">
+      <c r="E51" t="s">
         <v>659</v>
       </c>
-      <c r="F51" s="4">
+      <c r="F51" s="2">
         <v>16738</v>
       </c>
-      <c r="G51" s="3">
+      <c r="G51">
         <v>80</v>
       </c>
-      <c r="H51" s="3" t="s">
+      <c r="H51" t="s">
         <v>951</v>
       </c>
-      <c r="I51" s="3" t="s">
+      <c r="I51" t="s">
         <v>17</v>
       </c>
-      <c r="J51" s="3">
+      <c r="J51">
         <v>989723254</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A52" s="4">
+      <c r="A52" s="2">
         <v>46220</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="B52" t="s">
         <v>175</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="C52" t="s">
         <v>178</v>
       </c>
-      <c r="D52" s="3" t="s">
+      <c r="D52" t="s">
         <v>392</v>
       </c>
-      <c r="E52" s="3" t="s">
+      <c r="E52" t="s">
         <v>660</v>
       </c>
-      <c r="F52" s="4">
+      <c r="F52" s="2">
         <v>24785</v>
       </c>
-      <c r="G52" s="3">
+      <c r="G52">
         <v>58</v>
       </c>
-      <c r="H52" s="3" t="s">
+      <c r="H52" t="s">
         <v>261</v>
       </c>
-      <c r="I52" s="3" t="s">
+      <c r="I52" t="s">
         <v>17</v>
       </c>
-      <c r="J52" s="3">
+      <c r="J52">
         <v>940401158</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A53" s="4">
+      <c r="A53" s="2">
         <v>46220</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="B53" t="s">
         <v>175</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="C53" t="s">
         <v>178</v>
       </c>
-      <c r="D53" s="3" t="s">
+      <c r="D53" t="s">
         <v>393</v>
       </c>
-      <c r="E53" s="3" t="s">
+      <c r="E53" t="s">
         <v>661</v>
       </c>
-      <c r="F53" s="4">
+      <c r="F53" s="2">
         <v>18712</v>
       </c>
-      <c r="G53" s="3">
+      <c r="G53">
         <v>75</v>
       </c>
-      <c r="H53" s="3" t="s">
+      <c r="H53" t="s">
         <v>196</v>
       </c>
-      <c r="I53" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J53" s="3">
+      <c r="I53" t="s">
+        <v>9</v>
+      </c>
+      <c r="J53">
         <v>933481466</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A54" s="4">
+      <c r="A54" s="2">
         <v>46220</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="B54" t="s">
         <v>175</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="C54" t="s">
         <v>178</v>
       </c>
-      <c r="D54" s="3" t="s">
+      <c r="D54" t="s">
         <v>394</v>
       </c>
-      <c r="E54" s="3" t="s">
+      <c r="E54" t="s">
         <v>662</v>
       </c>
-      <c r="F54" s="4">
+      <c r="F54" s="2">
         <v>13112</v>
       </c>
-      <c r="G54" s="3">
+      <c r="G54">
         <v>90</v>
       </c>
-      <c r="H54" s="3" t="s">
+      <c r="H54" t="s">
         <v>218</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J54" s="3" t="s">
+      <c r="I54" t="s">
+        <v>9</v>
+      </c>
+      <c r="J54" t="s">
         <v>952</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A55" s="4">
+      <c r="A55" s="2">
         <v>46220</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="B55" t="s">
         <v>175</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="C55" t="s">
         <v>178</v>
       </c>
-      <c r="D55" s="3" t="s">
+      <c r="D55" t="s">
         <v>395</v>
       </c>
-      <c r="E55" s="3" t="s">
+      <c r="E55" t="s">
         <v>663</v>
       </c>
-      <c r="F55" s="4">
+      <c r="F55" s="2">
         <v>14784</v>
       </c>
-      <c r="G55" s="3">
+      <c r="G55">
         <v>86</v>
       </c>
-      <c r="H55" s="3" t="s">
+      <c r="H55" t="s">
         <v>87</v>
       </c>
-      <c r="I55" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J55" s="3">
+      <c r="I55" t="s">
+        <v>9</v>
+      </c>
+      <c r="J55">
         <v>997169772</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A56" s="4">
+      <c r="A56" s="2">
         <v>46220</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="B56" t="s">
         <v>175</v>
       </c>
-      <c r="C56" s="3" t="s">
+      <c r="C56" t="s">
         <v>178</v>
       </c>
-      <c r="D56" s="3" t="s">
+      <c r="D56" t="s">
         <v>396</v>
       </c>
-      <c r="E56" s="3" t="s">
+      <c r="E56" t="s">
         <v>664</v>
       </c>
-      <c r="F56" s="4">
+      <c r="F56" s="2">
         <v>17172</v>
       </c>
-      <c r="G56" s="3">
+      <c r="G56">
         <v>79</v>
       </c>
-      <c r="H56" s="3" t="s">
+      <c r="H56" t="s">
         <v>45</v>
       </c>
-      <c r="I56" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J56" s="3">
+      <c r="I56" t="s">
+        <v>9</v>
+      </c>
+      <c r="J56">
         <v>974590051</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A57" s="4">
+      <c r="A57" s="2">
         <v>46220</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="B57" t="s">
         <v>175</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="C57" t="s">
         <v>178</v>
       </c>
-      <c r="D57" s="3" t="s">
+      <c r="D57" t="s">
         <v>397</v>
       </c>
-      <c r="E57" s="3" t="s">
+      <c r="E57" t="s">
         <v>665</v>
       </c>
-      <c r="F57" s="4">
+      <c r="F57" s="2">
         <v>12709</v>
       </c>
-      <c r="G57" s="3">
+      <c r="G57">
         <v>91</v>
       </c>
-      <c r="H57" s="3" t="s">
+      <c r="H57" t="s">
         <v>218</v>
       </c>
-      <c r="I57" s="3" t="s">
+      <c r="I57" t="s">
         <v>17</v>
       </c>
-      <c r="J57" s="3">
+      <c r="J57">
         <v>999651251</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A58" s="4">
+      <c r="A58" s="2">
         <v>46220</v>
       </c>
-      <c r="B58" s="3" t="s">
+      <c r="B58" t="s">
         <v>175</v>
       </c>
-      <c r="C58" s="3" t="s">
+      <c r="C58" t="s">
         <v>178</v>
       </c>
-      <c r="D58" s="3" t="s">
+      <c r="D58" t="s">
         <v>398</v>
       </c>
-      <c r="E58" s="3" t="s">
+      <c r="E58" t="s">
         <v>666</v>
       </c>
-      <c r="F58" s="4">
+      <c r="F58" s="2">
         <v>14910</v>
       </c>
-      <c r="G58" s="3">
+      <c r="G58">
         <v>85</v>
       </c>
-      <c r="H58" s="3" t="s">
+      <c r="H58" t="s">
         <v>90</v>
       </c>
-      <c r="I58" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J58" s="3">
+      <c r="I58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J58">
         <v>955167308</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A59" s="4">
+      <c r="A59" s="2">
         <v>46220</v>
       </c>
-      <c r="B59" s="3" t="s">
+      <c r="B59" t="s">
         <v>175</v>
       </c>
-      <c r="C59" s="3" t="s">
+      <c r="C59" t="s">
         <v>178</v>
       </c>
-      <c r="D59" s="3" t="s">
+      <c r="D59" t="s">
         <v>399</v>
       </c>
-      <c r="E59" s="3" t="s">
+      <c r="E59" t="s">
         <v>667</v>
       </c>
-      <c r="F59" s="4">
+      <c r="F59" s="2">
         <v>18198</v>
       </c>
-      <c r="G59" s="3">
+      <c r="G59">
         <v>76</v>
       </c>
-      <c r="H59" s="3" t="s">
+      <c r="H59" t="s">
         <v>261</v>
       </c>
-      <c r="I59" s="3" t="s">
+      <c r="I59" t="s">
         <v>17</v>
       </c>
-      <c r="J59" s="3">
+      <c r="J59">
         <v>984395548</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A60" s="4">
+      <c r="A60" s="2">
         <v>46220</v>
       </c>
-      <c r="B60" s="3" t="s">
+      <c r="B60" t="s">
         <v>175</v>
       </c>
-      <c r="C60" s="3" t="s">
+      <c r="C60" t="s">
         <v>178</v>
       </c>
-      <c r="D60" s="3" t="s">
+      <c r="D60" t="s">
         <v>400</v>
       </c>
-      <c r="E60" s="3" t="s">
+      <c r="E60" t="s">
         <v>668</v>
       </c>
-      <c r="F60" s="4">
+      <c r="F60" s="2">
         <v>18726</v>
       </c>
-      <c r="G60" s="3">
+      <c r="G60">
         <v>75</v>
       </c>
-      <c r="H60" s="3" t="s">
+      <c r="H60" t="s">
         <v>11</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J60" s="3"/>
+      <c r="I60" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A61" s="4">
+      <c r="A61" s="2">
         <v>46220</v>
       </c>
-      <c r="B61" s="3" t="s">
+      <c r="B61" t="s">
         <v>175</v>
       </c>
-      <c r="C61" s="3" t="s">
+      <c r="C61" t="s">
         <v>178</v>
       </c>
-      <c r="D61" s="3" t="s">
+      <c r="D61" t="s">
         <v>219</v>
       </c>
-      <c r="E61" s="3" t="s">
+      <c r="E61" t="s">
         <v>217</v>
       </c>
-      <c r="F61" s="4">
+      <c r="F61" s="2">
         <v>24833</v>
       </c>
-      <c r="G61" s="3">
+      <c r="G61">
         <v>58</v>
       </c>
-      <c r="H61" s="3" t="s">
+      <c r="H61" t="s">
         <v>218</v>
       </c>
-      <c r="I61" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J61" s="3">
+      <c r="I61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J61">
         <v>964862531</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A62" s="4">
+      <c r="A62" s="2">
         <v>46223</v>
       </c>
-      <c r="B62" s="3" t="s">
+      <c r="B62" t="s">
         <v>175</v>
       </c>
-      <c r="C62" s="3" t="s">
+      <c r="C62" t="s">
         <v>179</v>
       </c>
-      <c r="D62" s="3" t="s">
+      <c r="D62" t="s">
         <v>401</v>
       </c>
-      <c r="E62" s="3" t="s">
+      <c r="E62" t="s">
         <v>669</v>
       </c>
-      <c r="F62" s="4">
+      <c r="F62" s="2">
         <v>30946</v>
       </c>
-      <c r="G62" s="3">
+      <c r="G62">
         <v>41</v>
       </c>
-      <c r="H62" s="3" t="s">
+      <c r="H62" t="s">
         <v>87</v>
       </c>
-      <c r="I62" s="3" t="s">
+      <c r="I62" t="s">
         <v>17</v>
       </c>
-      <c r="J62" s="3">
+      <c r="J62">
         <v>912145238</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A63" s="4">
+      <c r="A63" s="2">
         <v>46223</v>
       </c>
-      <c r="B63" s="3" t="s">
+      <c r="B63" t="s">
         <v>175</v>
       </c>
-      <c r="C63" s="3" t="s">
+      <c r="C63" t="s">
         <v>179</v>
       </c>
-      <c r="D63" s="3" t="s">
+      <c r="D63" t="s">
         <v>402</v>
       </c>
-      <c r="E63" s="3" t="s">
+      <c r="E63" t="s">
         <v>670</v>
       </c>
-      <c r="F63" s="4">
+      <c r="F63" s="2">
         <v>23242</v>
       </c>
-      <c r="G63" s="3">
+      <c r="G63">
         <v>62</v>
       </c>
-      <c r="H63" s="3" t="s">
+      <c r="H63" t="s">
         <v>42</v>
       </c>
-      <c r="I63" s="3" t="s">
+      <c r="I63" t="s">
         <v>17</v>
       </c>
-      <c r="J63" s="3">
+      <c r="J63">
         <v>997501243</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A64" s="4">
+      <c r="A64" s="2">
         <v>46223</v>
       </c>
-      <c r="B64" s="3" t="s">
+      <c r="B64" t="s">
         <v>175</v>
       </c>
-      <c r="C64" s="3" t="s">
+      <c r="C64" t="s">
         <v>179</v>
       </c>
-      <c r="D64" s="3" t="s">
+      <c r="D64" t="s">
         <v>403</v>
       </c>
-      <c r="E64" s="3" t="s">
+      <c r="E64" t="s">
         <v>671</v>
       </c>
-      <c r="F64" s="4">
+      <c r="F64" s="2">
         <v>31205</v>
       </c>
-      <c r="G64" s="3">
+      <c r="G64">
         <v>41</v>
       </c>
-      <c r="H64" s="3" t="s">
+      <c r="H64" t="s">
         <v>13</v>
       </c>
-      <c r="I64" s="3" t="s">
+      <c r="I64" t="s">
         <v>17</v>
       </c>
-      <c r="J64" s="3">
+      <c r="J64">
         <v>971444616</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A65" s="4">
+      <c r="A65" s="2">
         <v>46223</v>
       </c>
-      <c r="B65" s="3" t="s">
+      <c r="B65" t="s">
         <v>175</v>
       </c>
-      <c r="C65" s="3" t="s">
+      <c r="C65" t="s">
         <v>179</v>
       </c>
-      <c r="D65" s="3">
+      <c r="D65">
         <v>41542281</v>
       </c>
-      <c r="E65" s="3" t="s">
+      <c r="E65" t="s">
         <v>672</v>
       </c>
-      <c r="F65" s="4">
+      <c r="F65" s="2">
         <v>30274</v>
       </c>
-      <c r="G65" s="3">
+      <c r="G65">
         <v>43</v>
       </c>
-      <c r="H65" s="3" t="s">
+      <c r="H65" t="s">
         <v>58</v>
       </c>
-      <c r="I65" s="3" t="s">
+      <c r="I65" t="s">
         <v>17</v>
       </c>
-      <c r="J65" s="3">
+      <c r="J65">
         <v>994585579</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A66" s="4">
+      <c r="A66" s="2">
         <v>46223</v>
       </c>
-      <c r="B66" s="3" t="s">
+      <c r="B66" t="s">
         <v>175</v>
       </c>
-      <c r="C66" s="3" t="s">
+      <c r="C66" t="s">
         <v>179</v>
       </c>
-      <c r="D66" s="3" t="s">
+      <c r="D66" t="s">
         <v>221</v>
       </c>
-      <c r="E66" s="3" t="s">
+      <c r="E66" t="s">
         <v>220</v>
       </c>
-      <c r="F66" s="4">
+      <c r="F66" s="2">
         <v>34696</v>
       </c>
-      <c r="G66" s="3">
+      <c r="G66">
         <v>31</v>
       </c>
-      <c r="H66" s="3" t="s">
+      <c r="H66" t="s">
         <v>87</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J66" s="3">
+      <c r="I66" t="s">
+        <v>9</v>
+      </c>
+      <c r="J66">
         <v>995021501</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A67" s="4">
+      <c r="A67" s="2">
         <v>46223</v>
       </c>
-      <c r="B67" s="3" t="s">
+      <c r="B67" t="s">
         <v>175</v>
       </c>
-      <c r="C67" s="3" t="s">
+      <c r="C67" t="s">
         <v>179</v>
       </c>
-      <c r="D67" s="3" t="s">
+      <c r="D67" t="s">
         <v>404</v>
       </c>
-      <c r="E67" s="3" t="s">
+      <c r="E67" t="s">
         <v>673</v>
       </c>
-      <c r="F67" s="4">
+      <c r="F67" s="2">
         <v>34107</v>
       </c>
-      <c r="G67" s="3">
+      <c r="G67">
         <v>33</v>
       </c>
-      <c r="H67" s="3" t="s">
+      <c r="H67" t="s">
         <v>218</v>
       </c>
-      <c r="I67" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J67" s="3">
+      <c r="I67" t="s">
+        <v>9</v>
+      </c>
+      <c r="J67">
         <v>951708994</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A68" s="4">
+      <c r="A68" s="2">
         <v>46223</v>
       </c>
-      <c r="B68" s="3" t="s">
+      <c r="B68" t="s">
         <v>175</v>
       </c>
-      <c r="C68" s="3" t="s">
+      <c r="C68" t="s">
         <v>179</v>
       </c>
-      <c r="D68" s="3" t="s">
+      <c r="D68" t="s">
         <v>405</v>
       </c>
-      <c r="E68" s="3" t="s">
+      <c r="E68" t="s">
         <v>674</v>
       </c>
-      <c r="F68" s="4">
+      <c r="F68" s="2">
         <v>35521</v>
       </c>
-      <c r="G68" s="3">
+      <c r="G68">
         <v>29</v>
       </c>
-      <c r="H68" s="3" t="s">
+      <c r="H68" t="s">
         <v>38</v>
       </c>
-      <c r="I68" s="3" t="s">
+      <c r="I68" t="s">
         <v>17</v>
       </c>
-      <c r="J68" s="3">
+      <c r="J68">
         <v>961775329</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A69" s="4">
+      <c r="A69" s="2">
         <v>46223</v>
       </c>
-      <c r="B69" s="3" t="s">
+      <c r="B69" t="s">
         <v>175</v>
       </c>
-      <c r="C69" s="3" t="s">
+      <c r="C69" t="s">
         <v>179</v>
       </c>
-      <c r="D69" s="3" t="s">
+      <c r="D69" t="s">
         <v>222</v>
       </c>
-      <c r="E69" s="3" t="s">
+      <c r="E69" t="s">
         <v>223</v>
       </c>
-      <c r="F69" s="4">
+      <c r="F69" s="2">
         <v>30950</v>
       </c>
-      <c r="G69" s="3">
+      <c r="G69">
         <v>41</v>
       </c>
-      <c r="H69" s="3" t="s">
+      <c r="H69" t="s">
         <v>38</v>
       </c>
-      <c r="I69" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J69" s="3">
+      <c r="I69" t="s">
+        <v>9</v>
+      </c>
+      <c r="J69">
         <v>987749075</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A70" s="4">
+      <c r="A70" s="2">
         <v>46223</v>
       </c>
-      <c r="B70" s="3" t="s">
+      <c r="B70" t="s">
         <v>175</v>
       </c>
-      <c r="C70" s="3" t="s">
+      <c r="C70" t="s">
         <v>179</v>
       </c>
-      <c r="D70" s="3" t="s">
+      <c r="D70" t="s">
         <v>406</v>
       </c>
-      <c r="E70" s="3" t="s">
+      <c r="E70" t="s">
         <v>675</v>
       </c>
-      <c r="F70" s="4">
+      <c r="F70" s="2">
         <v>31224</v>
       </c>
-      <c r="G70" s="3">
+      <c r="G70">
         <v>41</v>
       </c>
-      <c r="H70" s="3" t="s">
+      <c r="H70" t="s">
         <v>8</v>
       </c>
-      <c r="I70" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J70" s="3">
+      <c r="I70" t="s">
+        <v>9</v>
+      </c>
+      <c r="J70">
         <v>987731438</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A71" s="4">
+      <c r="A71" s="2">
         <v>46223</v>
       </c>
-      <c r="B71" s="3" t="s">
+      <c r="B71" t="s">
         <v>175</v>
       </c>
-      <c r="C71" s="3" t="s">
+      <c r="C71" t="s">
         <v>179</v>
       </c>
-      <c r="D71" s="3" t="s">
+      <c r="D71" t="s">
         <v>407</v>
       </c>
-      <c r="E71" s="3" t="s">
+      <c r="E71" t="s">
         <v>676</v>
       </c>
-      <c r="F71" s="4">
+      <c r="F71" s="2">
         <v>23557</v>
       </c>
-      <c r="G71" s="3">
+      <c r="G71">
         <v>62</v>
       </c>
-      <c r="H71" s="3" t="s">
+      <c r="H71" t="s">
         <v>38</v>
       </c>
-      <c r="I71" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J71" s="3">
+      <c r="I71" t="s">
+        <v>9</v>
+      </c>
+      <c r="J71">
         <v>993074536</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A72" s="4">
+      <c r="A72" s="2">
         <v>46223</v>
       </c>
-      <c r="B72" s="3" t="s">
+      <c r="B72" t="s">
         <v>175</v>
       </c>
-      <c r="C72" s="3" t="s">
+      <c r="C72" t="s">
         <v>179</v>
       </c>
-      <c r="D72" s="3" t="s">
+      <c r="D72" t="s">
         <v>408</v>
       </c>
-      <c r="E72" s="3" t="s">
+      <c r="E72" t="s">
         <v>677</v>
       </c>
-      <c r="F72" s="4">
+      <c r="F72" s="2">
         <v>30452</v>
       </c>
-      <c r="G72" s="3">
+      <c r="G72">
         <v>43</v>
       </c>
-      <c r="H72" s="3" t="s">
+      <c r="H72" t="s">
         <v>45</v>
       </c>
-      <c r="I72" s="3" t="s">
+      <c r="I72" t="s">
         <v>17</v>
       </c>
-      <c r="J72" s="3">
+      <c r="J72">
         <v>995758023</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A73" s="4">
+      <c r="A73" s="2">
         <v>46223</v>
       </c>
-      <c r="B73" s="3" t="s">
+      <c r="B73" t="s">
         <v>175</v>
       </c>
-      <c r="C73" s="3" t="s">
+      <c r="C73" t="s">
         <v>179</v>
       </c>
-      <c r="D73" s="3" t="s">
+      <c r="D73" t="s">
         <v>409</v>
       </c>
-      <c r="E73" s="3" t="s">
+      <c r="E73" t="s">
         <v>678</v>
       </c>
-      <c r="F73" s="4">
+      <c r="F73" s="2">
         <v>27093</v>
       </c>
-      <c r="G73" s="3">
+      <c r="G73">
         <v>52</v>
       </c>
-      <c r="H73" s="3" t="s">
+      <c r="H73" t="s">
         <v>196</v>
       </c>
-      <c r="I73" s="3" t="s">
+      <c r="I73" t="s">
         <v>17</v>
       </c>
-      <c r="J73" s="3">
+      <c r="J73">
         <v>997501242</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A74" s="4">
+      <c r="A74" s="2">
         <v>46223</v>
       </c>
-      <c r="B74" s="3" t="s">
+      <c r="B74" t="s">
         <v>175</v>
       </c>
-      <c r="C74" s="3" t="s">
+      <c r="C74" t="s">
         <v>179</v>
       </c>
-      <c r="D74" s="3" t="s">
+      <c r="D74" t="s">
         <v>410</v>
       </c>
-      <c r="E74" s="3" t="s">
+      <c r="E74" t="s">
         <v>679</v>
       </c>
-      <c r="F74" s="4">
+      <c r="F74" s="2">
         <v>31713</v>
       </c>
-      <c r="G74" s="3">
+      <c r="G74">
         <v>39</v>
       </c>
-      <c r="H74" s="3" t="s">
+      <c r="H74" t="s">
         <v>137</v>
       </c>
-      <c r="I74" s="3" t="s">
+      <c r="I74" t="s">
         <v>17</v>
       </c>
-      <c r="J74" s="3">
+      <c r="J74">
         <v>996045316</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A75" s="4">
+      <c r="A75" s="2">
         <v>46223</v>
       </c>
-      <c r="B75" s="3" t="s">
+      <c r="B75" t="s">
         <v>175</v>
       </c>
-      <c r="C75" s="3" t="s">
+      <c r="C75" t="s">
         <v>179</v>
       </c>
-      <c r="D75" s="3" t="s">
+      <c r="D75" t="s">
         <v>411</v>
       </c>
-      <c r="E75" s="3" t="s">
+      <c r="E75" t="s">
         <v>680</v>
       </c>
-      <c r="F75" s="4">
+      <c r="F75" s="2">
         <v>35875</v>
       </c>
-      <c r="G75" s="3">
+      <c r="G75">
         <v>28</v>
       </c>
-      <c r="H75" s="3" t="s">
+      <c r="H75" t="s">
         <v>45</v>
       </c>
-      <c r="I75" s="3" t="s">
+      <c r="I75" t="s">
         <v>17</v>
       </c>
-      <c r="J75" s="3">
+      <c r="J75">
         <v>941757519</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A76" s="4">
+      <c r="A76" s="2">
         <v>46223</v>
       </c>
-      <c r="B76" s="3" t="s">
+      <c r="B76" t="s">
         <v>175</v>
       </c>
-      <c r="C76" s="3" t="s">
+      <c r="C76" t="s">
         <v>179</v>
       </c>
-      <c r="D76" s="3" t="s">
+      <c r="D76" t="s">
         <v>412</v>
       </c>
-      <c r="E76" s="3" t="s">
+      <c r="E76" t="s">
         <v>681</v>
       </c>
-      <c r="F76" s="4">
+      <c r="F76" s="2">
         <v>32194</v>
       </c>
-      <c r="G76" s="3">
+      <c r="G76">
         <v>38</v>
       </c>
-      <c r="H76" s="3" t="s">
+      <c r="H76" t="s">
         <v>953</v>
       </c>
-      <c r="I76" s="3" t="s">
+      <c r="I76" t="s">
         <v>17</v>
       </c>
-      <c r="J76" s="3">
+      <c r="J76">
         <v>993100587</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A77" s="4">
+      <c r="A77" s="2">
         <v>46223</v>
       </c>
-      <c r="B77" s="3" t="s">
+      <c r="B77" t="s">
         <v>175</v>
       </c>
-      <c r="C77" s="3" t="s">
+      <c r="C77" t="s">
         <v>179</v>
       </c>
-      <c r="D77" s="3" t="s">
+      <c r="D77" t="s">
         <v>413</v>
       </c>
-      <c r="E77" s="3" t="s">
+      <c r="E77" t="s">
         <v>682</v>
       </c>
-      <c r="F77" s="4">
+      <c r="F77" s="2">
         <v>33474</v>
       </c>
-      <c r="G77" s="3">
+      <c r="G77">
         <v>34</v>
       </c>
-      <c r="H77" s="3" t="s">
+      <c r="H77" t="s">
         <v>36</v>
       </c>
-      <c r="I77" s="3" t="s">
+      <c r="I77" t="s">
         <v>17</v>
       </c>
-      <c r="J77" s="3">
+      <c r="J77">
         <v>966418822</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A78" s="4">
+      <c r="A78" s="2">
         <v>46223</v>
       </c>
-      <c r="B78" s="3" t="s">
+      <c r="B78" t="s">
         <v>175</v>
       </c>
-      <c r="C78" s="3" t="s">
+      <c r="C78" t="s">
         <v>179</v>
       </c>
-      <c r="D78" s="3" t="s">
+      <c r="D78" t="s">
         <v>225</v>
       </c>
-      <c r="E78" s="3" t="s">
+      <c r="E78" t="s">
         <v>224</v>
       </c>
-      <c r="F78" s="4">
+      <c r="F78" s="2">
         <v>28081</v>
       </c>
-      <c r="G78" s="3">
+      <c r="G78">
         <v>49</v>
       </c>
-      <c r="H78" s="3" t="s">
+      <c r="H78" t="s">
         <v>38</v>
       </c>
-      <c r="I78" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J78" s="3">
+      <c r="I78" t="s">
+        <v>9</v>
+      </c>
+      <c r="J78">
         <v>997516878</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A79" s="4">
+      <c r="A79" s="2">
         <v>46223</v>
       </c>
-      <c r="B79" s="3" t="s">
+      <c r="B79" t="s">
         <v>175</v>
       </c>
-      <c r="C79" s="3" t="s">
+      <c r="C79" t="s">
         <v>179</v>
       </c>
-      <c r="D79" s="3" t="s">
+      <c r="D79" t="s">
         <v>414</v>
       </c>
-      <c r="E79" s="3" t="s">
+      <c r="E79" t="s">
         <v>683</v>
       </c>
-      <c r="F79" s="4">
+      <c r="F79" s="2">
         <v>37440</v>
       </c>
-      <c r="G79" s="3">
+      <c r="G79">
         <v>24</v>
       </c>
-      <c r="H79" s="3" t="s">
+      <c r="H79" t="s">
         <v>38</v>
       </c>
-      <c r="I79" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J79" s="3">
+      <c r="I79" t="s">
+        <v>9</v>
+      </c>
+      <c r="J79">
         <v>923279333</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A80" s="4">
+      <c r="A80" s="2">
         <v>46223</v>
       </c>
-      <c r="B80" s="3" t="s">
+      <c r="B80" t="s">
         <v>175</v>
       </c>
-      <c r="C80" s="3" t="s">
+      <c r="C80" t="s">
         <v>179</v>
       </c>
-      <c r="D80" s="3" t="s">
+      <c r="D80" t="s">
         <v>415</v>
       </c>
-      <c r="E80" s="3" t="s">
+      <c r="E80" t="s">
         <v>684</v>
       </c>
-      <c r="F80" s="4">
+      <c r="F80" s="2">
         <v>35602</v>
       </c>
-      <c r="G80" s="3">
+      <c r="G80">
         <v>29</v>
       </c>
-      <c r="H80" s="3" t="s">
+      <c r="H80" t="s">
         <v>135</v>
       </c>
-      <c r="I80" s="3" t="s">
+      <c r="I80" t="s">
         <v>17</v>
       </c>
-      <c r="J80" s="3">
+      <c r="J80">
         <v>960667837</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A81" s="4">
+      <c r="A81" s="2">
         <v>46223</v>
       </c>
-      <c r="B81" s="3" t="s">
+      <c r="B81" t="s">
         <v>175</v>
       </c>
-      <c r="C81" s="3" t="s">
+      <c r="C81" t="s">
         <v>179</v>
       </c>
-      <c r="D81" s="3" t="s">
+      <c r="D81" t="s">
         <v>416</v>
       </c>
-      <c r="E81" s="3" t="s">
+      <c r="E81" t="s">
         <v>685</v>
       </c>
-      <c r="F81" s="4">
+      <c r="F81" s="2">
         <v>36595</v>
       </c>
-      <c r="G81" s="3">
+      <c r="G81">
         <v>26</v>
       </c>
-      <c r="H81" s="3" t="s">
+      <c r="H81" t="s">
         <v>155</v>
       </c>
-      <c r="I81" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J81" s="3">
+      <c r="I81" t="s">
+        <v>9</v>
+      </c>
+      <c r="J81">
         <v>944866386</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A82" s="4">
+      <c r="A82" s="2">
         <v>46223</v>
       </c>
-      <c r="B82" s="3" t="s">
+      <c r="B82" t="s">
         <v>175</v>
       </c>
-      <c r="C82" s="3" t="s">
+      <c r="C82" t="s">
         <v>179</v>
       </c>
-      <c r="D82" s="3" t="s">
+      <c r="D82" t="s">
         <v>417</v>
       </c>
-      <c r="E82" s="3" t="s">
+      <c r="E82" t="s">
         <v>686</v>
       </c>
-      <c r="F82" s="4">
+      <c r="F82" s="2">
         <v>36789</v>
       </c>
-      <c r="G82" s="3">
+      <c r="G82">
         <v>25</v>
       </c>
-      <c r="H82" s="3" t="s">
+      <c r="H82" t="s">
         <v>92</v>
       </c>
-      <c r="I82" s="3" t="s">
+      <c r="I82" t="s">
         <v>17</v>
       </c>
-      <c r="J82" s="3">
+      <c r="J82">
         <v>912476082</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A83" s="4">
+      <c r="A83" s="2">
         <v>46223</v>
       </c>
-      <c r="B83" s="3" t="s">
+      <c r="B83" t="s">
         <v>175</v>
       </c>
-      <c r="C83" s="3" t="s">
+      <c r="C83" t="s">
         <v>179</v>
       </c>
-      <c r="D83" s="3" t="s">
+      <c r="D83" t="s">
         <v>418</v>
       </c>
-      <c r="E83" s="3" t="s">
+      <c r="E83" t="s">
         <v>687</v>
       </c>
-      <c r="F83" s="4">
+      <c r="F83" s="2">
         <v>34357</v>
       </c>
-      <c r="G83" s="3">
+      <c r="G83">
         <v>32</v>
       </c>
-      <c r="H83" s="3" t="s">
+      <c r="H83" t="s">
         <v>954</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J83" s="3">
+      <c r="I83" t="s">
+        <v>9</v>
+      </c>
+      <c r="J83">
         <v>997512939</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A84" s="4">
+      <c r="A84" s="2">
         <v>46223</v>
       </c>
-      <c r="B84" s="3" t="s">
+      <c r="B84" t="s">
         <v>175</v>
       </c>
-      <c r="C84" s="3" t="s">
+      <c r="C84" t="s">
         <v>179</v>
       </c>
-      <c r="D84" s="3" t="s">
+      <c r="D84" t="s">
         <v>419</v>
       </c>
-      <c r="E84" s="3" t="s">
+      <c r="E84" t="s">
         <v>688</v>
       </c>
-      <c r="F84" s="4">
+      <c r="F84" s="2">
         <v>37461</v>
       </c>
-      <c r="G84" s="3">
+      <c r="G84">
         <v>24</v>
       </c>
-      <c r="H84" s="3" t="s">
+      <c r="H84" t="s">
         <v>162</v>
       </c>
-      <c r="I84" s="3" t="s">
+      <c r="I84" t="s">
         <v>17</v>
       </c>
-      <c r="J84" s="3">
+      <c r="J84">
         <v>963855444</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A85" s="4">
+      <c r="A85" s="2">
         <v>46223</v>
       </c>
-      <c r="B85" s="3" t="s">
+      <c r="B85" t="s">
         <v>175</v>
       </c>
-      <c r="C85" s="3" t="s">
+      <c r="C85" t="s">
         <v>179</v>
       </c>
-      <c r="D85" s="3" t="s">
+      <c r="D85" t="s">
         <v>420</v>
       </c>
-      <c r="E85" s="3" t="s">
+      <c r="E85" t="s">
         <v>689</v>
       </c>
-      <c r="F85" s="4">
+      <c r="F85" s="2">
         <v>34322</v>
       </c>
-      <c r="G85" s="3">
+      <c r="G85">
         <v>32</v>
       </c>
-      <c r="H85" s="3" t="s">
+      <c r="H85" t="s">
         <v>261</v>
       </c>
-      <c r="I85" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J85" s="3">
+      <c r="I85" t="s">
+        <v>9</v>
+      </c>
+      <c r="J85">
         <v>993349171</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A86" s="4">
+      <c r="A86" s="2">
         <v>46223</v>
       </c>
-      <c r="B86" s="3" t="s">
+      <c r="B86" t="s">
         <v>175</v>
       </c>
-      <c r="C86" s="3" t="s">
+      <c r="C86" t="s">
         <v>179</v>
       </c>
-      <c r="D86" s="3" t="s">
+      <c r="D86" t="s">
         <v>421</v>
       </c>
-      <c r="E86" s="3" t="s">
+      <c r="E86" t="s">
         <v>690</v>
       </c>
-      <c r="F86" s="4">
+      <c r="F86" s="2">
         <v>34723</v>
       </c>
-      <c r="G86" s="3">
+      <c r="G86">
         <v>31</v>
       </c>
-      <c r="H86" s="3" t="s">
+      <c r="H86" t="s">
         <v>90</v>
       </c>
-      <c r="I86" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J86" s="3">
+      <c r="I86" t="s">
+        <v>9</v>
+      </c>
+      <c r="J86">
         <v>948948456</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A87" s="4">
+      <c r="A87" s="2">
         <v>46223</v>
       </c>
-      <c r="B87" s="3" t="s">
+      <c r="B87" t="s">
         <v>175</v>
       </c>
-      <c r="C87" s="3" t="s">
+      <c r="C87" t="s">
         <v>179</v>
       </c>
-      <c r="D87" s="3" t="s">
+      <c r="D87" t="s">
         <v>422</v>
       </c>
-      <c r="E87" s="3" t="s">
+      <c r="E87" t="s">
         <v>691</v>
       </c>
-      <c r="F87" s="4">
+      <c r="F87" s="2">
         <v>37773</v>
       </c>
-      <c r="G87" s="3">
+      <c r="G87">
         <v>23</v>
       </c>
-      <c r="H87" s="3" t="s">
+      <c r="H87" t="s">
         <v>81</v>
       </c>
-      <c r="I87" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J87" s="3">
+      <c r="I87" t="s">
+        <v>9</v>
+      </c>
+      <c r="J87">
         <v>933732897</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A88" s="4">
+      <c r="A88" s="2">
         <v>46223</v>
       </c>
-      <c r="B88" s="3" t="s">
+      <c r="B88" t="s">
         <v>175</v>
       </c>
-      <c r="C88" s="3" t="s">
+      <c r="C88" t="s">
         <v>179</v>
       </c>
-      <c r="D88" s="3" t="s">
+      <c r="D88" t="s">
         <v>423</v>
       </c>
-      <c r="E88" s="3" t="s">
+      <c r="E88" t="s">
         <v>692</v>
       </c>
-      <c r="F88" s="4">
+      <c r="F88" s="2">
         <v>37538</v>
       </c>
-      <c r="G88" s="3">
+      <c r="G88">
         <v>23</v>
       </c>
-      <c r="H88" s="3" t="s">
+      <c r="H88" t="s">
         <v>90</v>
       </c>
-      <c r="I88" s="3" t="s">
+      <c r="I88" t="s">
         <v>17</v>
       </c>
-      <c r="J88" s="3">
+      <c r="J88">
         <v>965775072</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A89" s="4">
+      <c r="A89" s="2">
         <v>46223</v>
       </c>
-      <c r="B89" s="3" t="s">
+      <c r="B89" t="s">
         <v>175</v>
       </c>
-      <c r="C89" s="3" t="s">
+      <c r="C89" t="s">
         <v>179</v>
       </c>
-      <c r="D89" s="3" t="s">
+      <c r="D89" t="s">
         <v>424</v>
       </c>
-      <c r="E89" s="3" t="s">
+      <c r="E89" t="s">
         <v>693</v>
       </c>
-      <c r="F89" s="4">
+      <c r="F89" s="2">
         <v>37563</v>
       </c>
-      <c r="G89" s="3">
+      <c r="G89">
         <v>23</v>
       </c>
-      <c r="H89" s="3" t="s">
+      <c r="H89" t="s">
         <v>196</v>
       </c>
-      <c r="I89" s="3" t="s">
+      <c r="I89" t="s">
         <v>17</v>
       </c>
-      <c r="J89" s="3">
+      <c r="J89">
         <v>989922573</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A90" s="4">
+      <c r="A90" s="2">
         <v>46223</v>
       </c>
-      <c r="B90" s="3" t="s">
+      <c r="B90" t="s">
         <v>175</v>
       </c>
-      <c r="C90" s="3" t="s">
+      <c r="C90" t="s">
         <v>179</v>
       </c>
-      <c r="D90" s="3" t="s">
+      <c r="D90" t="s">
         <v>425</v>
       </c>
-      <c r="E90" s="3" t="s">
+      <c r="E90" t="s">
         <v>694</v>
       </c>
-      <c r="F90" s="4">
+      <c r="F90" s="2">
         <v>37142</v>
       </c>
-      <c r="G90" s="3">
+      <c r="G90">
         <v>24</v>
       </c>
-      <c r="H90" s="3" t="s">
+      <c r="H90" t="s">
         <v>38</v>
       </c>
-      <c r="I90" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J90" s="3">
+      <c r="I90" t="s">
+        <v>9</v>
+      </c>
+      <c r="J90">
         <v>961583443</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A91" s="4">
+      <c r="A91" s="2">
         <v>46223</v>
       </c>
-      <c r="B91" s="3" t="s">
+      <c r="B91" t="s">
         <v>175</v>
       </c>
-      <c r="C91" s="3" t="s">
+      <c r="C91" t="s">
         <v>179</v>
       </c>
-      <c r="D91" s="3" t="s">
+      <c r="D91" t="s">
         <v>426</v>
       </c>
-      <c r="E91" s="3" t="s">
+      <c r="E91" t="s">
         <v>695</v>
       </c>
-      <c r="F91" s="4">
+      <c r="F91" s="2">
         <v>33179</v>
       </c>
-      <c r="G91" s="3">
+      <c r="G91">
         <v>35</v>
       </c>
-      <c r="H91" s="3" t="s">
+      <c r="H91" t="s">
         <v>162</v>
       </c>
-      <c r="I91" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J91" s="3">
+      <c r="I91" t="s">
+        <v>9</v>
+      </c>
+      <c r="J91">
         <v>993308131</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A92" s="4">
+      <c r="A92" s="2">
         <v>46223</v>
       </c>
-      <c r="B92" s="3" t="s">
+      <c r="B92" t="s">
         <v>175</v>
       </c>
-      <c r="C92" s="3" t="s">
+      <c r="C92" t="s">
         <v>179</v>
       </c>
-      <c r="D92" s="3" t="s">
+      <c r="D92" t="s">
         <v>427</v>
       </c>
-      <c r="E92" s="3" t="s">
+      <c r="E92" t="s">
         <v>696</v>
       </c>
-      <c r="F92" s="4">
+      <c r="F92" s="2">
         <v>32011</v>
       </c>
-      <c r="G92" s="3">
+      <c r="G92">
         <v>38</v>
       </c>
-      <c r="H92" s="3" t="s">
+      <c r="H92" t="s">
         <v>38</v>
       </c>
-      <c r="I92" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J92" s="3">
+      <c r="I92" t="s">
+        <v>9</v>
+      </c>
+      <c r="J92">
         <v>980710270</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A93" s="4">
+      <c r="A93" s="2">
         <v>46223</v>
       </c>
-      <c r="B93" s="3" t="s">
+      <c r="B93" t="s">
         <v>175</v>
       </c>
-      <c r="C93" s="3" t="s">
+      <c r="C93" t="s">
         <v>179</v>
       </c>
-      <c r="D93" s="3" t="s">
+      <c r="D93" t="s">
         <v>428</v>
       </c>
-      <c r="E93" s="3" t="s">
+      <c r="E93" t="s">
         <v>697</v>
       </c>
-      <c r="F93" s="4">
+      <c r="F93" s="2">
         <v>28325</v>
       </c>
-      <c r="G93" s="3">
+      <c r="G93">
         <v>49</v>
       </c>
-      <c r="H93" s="3" t="s">
+      <c r="H93" t="s">
         <v>8</v>
       </c>
-      <c r="I93" s="3" t="s">
+      <c r="I93" t="s">
         <v>17</v>
       </c>
-      <c r="J93" s="3">
+      <c r="J93">
         <v>994841488</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A94" s="4">
+      <c r="A94" s="2">
         <v>46223</v>
       </c>
-      <c r="B94" s="3" t="s">
+      <c r="B94" t="s">
         <v>175</v>
       </c>
-      <c r="C94" s="3" t="s">
+      <c r="C94" t="s">
         <v>179</v>
       </c>
-      <c r="D94" s="3" t="s">
+      <c r="D94" t="s">
         <v>429</v>
       </c>
-      <c r="E94" s="3" t="s">
+      <c r="E94" t="s">
         <v>698</v>
       </c>
-      <c r="F94" s="4">
+      <c r="F94" s="2">
         <v>36058</v>
       </c>
-      <c r="G94" s="3">
+      <c r="G94">
         <v>27</v>
       </c>
-      <c r="H94" s="3" t="s">
+      <c r="H94" t="s">
         <v>16</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J94" s="3">
+      <c r="I94" t="s">
+        <v>9</v>
+      </c>
+      <c r="J94">
         <v>912858664</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A95" s="4">
+      <c r="A95" s="2">
         <v>46223</v>
       </c>
-      <c r="B95" s="3" t="s">
+      <c r="B95" t="s">
         <v>175</v>
       </c>
-      <c r="C95" s="3" t="s">
+      <c r="C95" t="s">
         <v>179</v>
       </c>
-      <c r="D95" s="3" t="s">
+      <c r="D95" t="s">
         <v>229</v>
       </c>
-      <c r="E95" s="3" t="s">
+      <c r="E95" t="s">
         <v>228</v>
       </c>
-      <c r="F95" s="4">
+      <c r="F95" s="2">
         <v>33266</v>
       </c>
-      <c r="G95" s="3">
+      <c r="G95">
         <v>35</v>
       </c>
-      <c r="H95" s="3" t="s">
+      <c r="H95" t="s">
         <v>90</v>
       </c>
-      <c r="I95" s="3" t="s">
+      <c r="I95" t="s">
         <v>17</v>
       </c>
-      <c r="J95" s="3">
+      <c r="J95">
         <v>953736785</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A96" s="4">
+      <c r="A96" s="2">
         <v>46223</v>
       </c>
-      <c r="B96" s="3" t="s">
+      <c r="B96" t="s">
         <v>175</v>
       </c>
-      <c r="C96" s="3" t="s">
+      <c r="C96" t="s">
         <v>179</v>
       </c>
-      <c r="D96" s="3" t="s">
+      <c r="D96" t="s">
         <v>430</v>
       </c>
-      <c r="E96" s="3" t="s">
+      <c r="E96" t="s">
         <v>699</v>
       </c>
-      <c r="F96" s="4">
+      <c r="F96" s="2">
         <v>36318</v>
       </c>
-      <c r="G96" s="3">
+      <c r="G96">
         <v>27</v>
       </c>
-      <c r="H96" s="3" t="s">
+      <c r="H96" t="s">
         <v>8</v>
       </c>
-      <c r="I96" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J96" s="3">
+      <c r="I96" t="s">
+        <v>9</v>
+      </c>
+      <c r="J96">
         <v>977122537</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A97" s="4">
+      <c r="A97" s="2">
         <v>46223</v>
       </c>
-      <c r="B97" s="3" t="s">
+      <c r="B97" t="s">
         <v>175</v>
       </c>
-      <c r="C97" s="3" t="s">
+      <c r="C97" t="s">
         <v>179</v>
       </c>
-      <c r="D97" s="3" t="s">
+      <c r="D97" t="s">
         <v>431</v>
       </c>
-      <c r="E97" s="3" t="s">
+      <c r="E97" t="s">
         <v>700</v>
       </c>
-      <c r="F97" s="4">
+      <c r="F97" s="2">
         <v>35715</v>
       </c>
-      <c r="G97" s="3">
+      <c r="G97">
         <v>28</v>
       </c>
-      <c r="H97" s="3" t="s">
+      <c r="H97" t="s">
         <v>42</v>
       </c>
-      <c r="I97" s="3" t="s">
+      <c r="I97" t="s">
         <v>17</v>
       </c>
-      <c r="J97" s="3">
+      <c r="J97">
         <v>993588181</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A98" s="4">
+      <c r="A98" s="2">
         <v>46223</v>
       </c>
-      <c r="B98" s="3" t="s">
+      <c r="B98" t="s">
         <v>175</v>
       </c>
-      <c r="C98" s="3" t="s">
+      <c r="C98" t="s">
         <v>179</v>
       </c>
-      <c r="D98" s="3" t="s">
+      <c r="D98" t="s">
         <v>226</v>
       </c>
-      <c r="E98" s="3" t="s">
+      <c r="E98" t="s">
         <v>227</v>
       </c>
-      <c r="F98" s="4">
+      <c r="F98" s="2">
         <v>30821</v>
       </c>
-      <c r="G98" s="3">
+      <c r="G98">
         <v>42</v>
       </c>
-      <c r="H98" s="3" t="s">
+      <c r="H98" t="s">
         <v>38</v>
       </c>
-      <c r="I98" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J98" s="3">
+      <c r="I98" t="s">
+        <v>9</v>
+      </c>
+      <c r="J98">
         <v>980480037</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A99" s="4">
+      <c r="A99" s="2">
         <v>46223</v>
       </c>
-      <c r="B99" s="3" t="s">
+      <c r="B99" t="s">
         <v>175</v>
       </c>
-      <c r="C99" s="3" t="s">
+      <c r="C99" t="s">
         <v>179</v>
       </c>
-      <c r="D99" s="3" t="s">
+      <c r="D99" t="s">
         <v>432</v>
       </c>
-      <c r="E99" s="3" t="s">
+      <c r="E99" t="s">
         <v>701</v>
       </c>
-      <c r="F99" s="4">
+      <c r="F99" s="2">
         <v>35157</v>
       </c>
-      <c r="G99" s="3">
+      <c r="G99">
         <v>30</v>
       </c>
-      <c r="H99" s="3" t="s">
+      <c r="H99" t="s">
         <v>38</v>
       </c>
-      <c r="I99" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J99" s="3">
+      <c r="I99" t="s">
+        <v>9</v>
+      </c>
+      <c r="J99">
         <v>940205566</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A100" s="4">
+      <c r="A100" s="2">
         <v>46223</v>
       </c>
-      <c r="B100" s="3" t="s">
+      <c r="B100" t="s">
         <v>175</v>
       </c>
-      <c r="C100" s="3" t="s">
+      <c r="C100" t="s">
         <v>179</v>
       </c>
-      <c r="D100" s="3" t="s">
+      <c r="D100" t="s">
         <v>433</v>
       </c>
-      <c r="E100" s="3" t="s">
+      <c r="E100" t="s">
         <v>230</v>
       </c>
-      <c r="F100" s="4">
+      <c r="F100" s="2">
         <v>36191</v>
       </c>
-      <c r="G100" s="3">
+      <c r="G100">
         <v>27</v>
       </c>
-      <c r="H100" s="3" t="s">
+      <c r="H100" t="s">
         <v>36</v>
       </c>
-      <c r="I100" s="3" t="s">
+      <c r="I100" t="s">
         <v>17</v>
       </c>
-      <c r="J100" s="3">
+      <c r="J100">
         <v>981542005</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A101" s="4">
+      <c r="A101" s="2">
         <v>46223</v>
       </c>
-      <c r="B101" s="3" t="s">
+      <c r="B101" t="s">
         <v>175</v>
       </c>
-      <c r="C101" s="3" t="s">
+      <c r="C101" t="s">
         <v>179</v>
       </c>
-      <c r="D101" s="3" t="s">
+      <c r="D101" t="s">
         <v>434</v>
       </c>
-      <c r="E101" s="3" t="s">
+      <c r="E101" t="s">
         <v>702</v>
       </c>
-      <c r="F101" s="4">
+      <c r="F101" s="2">
         <v>31792</v>
       </c>
-      <c r="G101" s="3">
+      <c r="G101">
         <v>39</v>
       </c>
-      <c r="H101" s="3" t="s">
+      <c r="H101" t="s">
         <v>32</v>
       </c>
-      <c r="I101" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J101" s="3">
+      <c r="I101" t="s">
+        <v>9</v>
+      </c>
+      <c r="J101">
         <v>993688759</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A102" s="4">
+      <c r="A102" s="2">
         <v>46223</v>
       </c>
-      <c r="B102" s="3" t="s">
+      <c r="B102" t="s">
         <v>175</v>
       </c>
-      <c r="C102" s="3" t="s">
+      <c r="C102" t="s">
         <v>179</v>
       </c>
-      <c r="D102" s="3" t="s">
+      <c r="D102" t="s">
         <v>231</v>
       </c>
-      <c r="E102" s="3" t="s">
+      <c r="E102" t="s">
         <v>232</v>
       </c>
-      <c r="F102" s="4">
+      <c r="F102" s="2">
         <v>34801</v>
       </c>
-      <c r="G102" s="3">
+      <c r="G102">
         <v>31</v>
       </c>
-      <c r="H102" s="3" t="s">
+      <c r="H102" t="s">
         <v>92</v>
       </c>
-      <c r="I102" s="3" t="s">
+      <c r="I102" t="s">
         <v>17</v>
       </c>
-      <c r="J102" s="3">
+      <c r="J102">
         <v>941628100</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A103" s="4">
+      <c r="A103" s="2">
         <v>46223</v>
       </c>
-      <c r="B103" s="3" t="s">
+      <c r="B103" t="s">
         <v>175</v>
       </c>
-      <c r="C103" s="3" t="s">
+      <c r="C103" t="s">
         <v>179</v>
       </c>
-      <c r="D103" s="3" t="s">
+      <c r="D103" t="s">
         <v>435</v>
       </c>
-      <c r="E103" s="3" t="s">
+      <c r="E103" t="s">
         <v>703</v>
       </c>
-      <c r="F103" s="4">
+      <c r="F103" s="2">
         <v>35660</v>
       </c>
-      <c r="G103" s="3">
+      <c r="G103">
         <v>28</v>
       </c>
-      <c r="H103" s="3" t="s">
+      <c r="H103" t="s">
         <v>87</v>
       </c>
-      <c r="I103" s="3" t="s">
+      <c r="I103" t="s">
         <v>17</v>
       </c>
-      <c r="J103" s="3">
+      <c r="J103">
         <v>981255730</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A104" s="4">
+      <c r="A104" s="2">
         <v>46223</v>
       </c>
-      <c r="B104" s="3" t="s">
+      <c r="B104" t="s">
         <v>175</v>
       </c>
-      <c r="C104" s="3" t="s">
+      <c r="C104" t="s">
         <v>179</v>
       </c>
-      <c r="D104" s="3" t="s">
+      <c r="D104" t="s">
         <v>436</v>
       </c>
-      <c r="E104" s="3" t="s">
+      <c r="E104" t="s">
         <v>704</v>
       </c>
-      <c r="F104" s="4">
+      <c r="F104" s="2">
         <v>35428</v>
       </c>
-      <c r="G104" s="3">
+      <c r="G104">
         <v>29</v>
       </c>
-      <c r="H104" s="3" t="s">
+      <c r="H104" t="s">
         <v>92</v>
       </c>
-      <c r="I104" s="3" t="s">
+      <c r="I104" t="s">
         <v>17</v>
       </c>
-      <c r="J104" s="3">
+      <c r="J104">
         <v>927526409</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A105" s="4">
+      <c r="A105" s="2">
         <v>46223</v>
       </c>
-      <c r="B105" s="3" t="s">
+      <c r="B105" t="s">
         <v>175</v>
       </c>
-      <c r="C105" s="3" t="s">
+      <c r="C105" t="s">
         <v>179</v>
       </c>
-      <c r="D105" s="3" t="s">
+      <c r="D105" t="s">
         <v>437</v>
       </c>
-      <c r="E105" s="3" t="s">
+      <c r="E105" t="s">
         <v>705</v>
       </c>
-      <c r="F105" s="4">
+      <c r="F105" s="2">
         <v>33653</v>
       </c>
-      <c r="G105" s="3">
+      <c r="G105">
         <v>34</v>
       </c>
-      <c r="H105" s="3" t="s">
+      <c r="H105" t="s">
         <v>261</v>
       </c>
-      <c r="I105" s="3" t="s">
+      <c r="I105" t="s">
         <v>17</v>
       </c>
-      <c r="J105" s="3">
+      <c r="J105">
         <v>991169436</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A106" s="4">
+      <c r="A106" s="2">
         <v>46223</v>
       </c>
-      <c r="B106" s="3" t="s">
+      <c r="B106" t="s">
         <v>175</v>
       </c>
-      <c r="C106" s="3" t="s">
+      <c r="C106" t="s">
         <v>179</v>
       </c>
-      <c r="D106" s="3" t="s">
+      <c r="D106" t="s">
         <v>438</v>
       </c>
-      <c r="E106" s="3" t="s">
+      <c r="E106" t="s">
         <v>706</v>
       </c>
-      <c r="F106" s="4">
+      <c r="F106" s="2">
         <v>36100</v>
       </c>
-      <c r="G106" s="3">
+      <c r="G106">
         <v>27</v>
       </c>
-      <c r="H106" s="3" t="s">
+      <c r="H106" t="s">
         <v>92</v>
       </c>
-      <c r="I106" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J106" s="3">
+      <c r="I106" t="s">
+        <v>9</v>
+      </c>
+      <c r="J106">
         <v>923512853</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A107" s="4">
+      <c r="A107" s="2">
         <v>46223</v>
       </c>
-      <c r="B107" s="3" t="s">
+      <c r="B107" t="s">
         <v>175</v>
       </c>
-      <c r="C107" s="3" t="s">
+      <c r="C107" t="s">
         <v>179</v>
       </c>
-      <c r="D107" s="3" t="s">
+      <c r="D107" t="s">
         <v>439</v>
       </c>
-      <c r="E107" s="3" t="s">
+      <c r="E107" t="s">
         <v>707</v>
       </c>
-      <c r="F107" s="4">
+      <c r="F107" s="2">
         <v>34872</v>
       </c>
-      <c r="G107" s="3">
+      <c r="G107">
         <v>31</v>
       </c>
-      <c r="H107" s="3" t="s">
+      <c r="H107" t="s">
         <v>162</v>
       </c>
-      <c r="I107" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J107" s="3">
+      <c r="I107" t="s">
+        <v>9</v>
+      </c>
+      <c r="J107">
         <v>923965185</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A108" s="4">
+      <c r="A108" s="2">
         <v>46223</v>
       </c>
-      <c r="B108" s="3" t="s">
+      <c r="B108" t="s">
         <v>175</v>
       </c>
-      <c r="C108" s="3" t="s">
+      <c r="C108" t="s">
         <v>179</v>
       </c>
-      <c r="D108" s="3" t="s">
+      <c r="D108" t="s">
         <v>440</v>
       </c>
-      <c r="E108" s="3" t="s">
+      <c r="E108" t="s">
         <v>708</v>
       </c>
-      <c r="F108" s="4">
+      <c r="F108" s="2">
         <v>35497</v>
       </c>
-      <c r="G108" s="3">
+      <c r="G108">
         <v>29</v>
       </c>
-      <c r="H108" s="3" t="s">
+      <c r="H108" t="s">
         <v>87</v>
       </c>
-      <c r="I108" s="3" t="s">
+      <c r="I108" t="s">
         <v>17</v>
       </c>
-      <c r="J108" s="3">
+      <c r="J108">
         <v>976976537</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A109" s="4">
+      <c r="A109" s="2">
         <v>46223</v>
       </c>
-      <c r="B109" s="3" t="s">
+      <c r="B109" t="s">
         <v>175</v>
       </c>
-      <c r="C109" s="3" t="s">
+      <c r="C109" t="s">
         <v>179</v>
       </c>
-      <c r="D109" s="3" t="s">
+      <c r="D109" t="s">
         <v>441</v>
       </c>
-      <c r="E109" s="3" t="s">
+      <c r="E109" t="s">
         <v>709</v>
       </c>
-      <c r="F109" s="4">
+      <c r="F109" s="2">
         <v>35020</v>
       </c>
-      <c r="G109" s="3">
+      <c r="G109">
         <v>30</v>
       </c>
-      <c r="H109" s="3" t="s">
+      <c r="H109" t="s">
         <v>45</v>
       </c>
-      <c r="I109" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J109" s="3">
+      <c r="I109" t="s">
+        <v>9</v>
+      </c>
+      <c r="J109">
         <v>943264539</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A110" s="4">
+      <c r="A110" s="2">
         <v>46223</v>
       </c>
-      <c r="B110" s="3" t="s">
+      <c r="B110" t="s">
         <v>175</v>
       </c>
-      <c r="C110" s="3" t="s">
+      <c r="C110" t="s">
         <v>179</v>
       </c>
-      <c r="D110" s="3" t="s">
+      <c r="D110" t="s">
         <v>442</v>
       </c>
-      <c r="E110" s="3" t="s">
+      <c r="E110" t="s">
         <v>710</v>
       </c>
-      <c r="F110" s="4">
+      <c r="F110" s="2">
         <v>32640</v>
       </c>
-      <c r="G110" s="3">
+      <c r="G110">
         <v>37</v>
       </c>
-      <c r="H110" s="3" t="s">
+      <c r="H110" t="s">
         <v>16</v>
       </c>
-      <c r="I110" s="3" t="s">
+      <c r="I110" t="s">
         <v>17</v>
       </c>
-      <c r="J110" s="3">
+      <c r="J110">
         <v>947120518</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A111" s="4">
+      <c r="A111" s="2">
         <v>46227</v>
       </c>
-      <c r="B111" s="3" t="s">
+      <c r="B111" t="s">
         <v>175</v>
       </c>
-      <c r="C111" s="3" t="s">
+      <c r="C111" t="s">
         <v>180</v>
       </c>
-      <c r="D111" s="3" t="s">
+      <c r="D111" t="s">
         <v>443</v>
       </c>
-      <c r="E111" s="3" t="s">
+      <c r="E111" t="s">
         <v>711</v>
       </c>
-      <c r="F111" s="4">
+      <c r="F111" s="2">
         <v>35374</v>
       </c>
-      <c r="G111" s="3">
+      <c r="G111">
         <v>29</v>
       </c>
-      <c r="H111" s="3" t="s">
+      <c r="H111" t="s">
         <v>30</v>
       </c>
-      <c r="I111" s="3" t="s">
+      <c r="I111" t="s">
         <v>17</v>
       </c>
-      <c r="J111" s="3">
+      <c r="J111">
         <v>962721482</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A112" s="4">
+      <c r="A112" s="2">
         <v>46227</v>
       </c>
-      <c r="B112" s="3" t="s">
+      <c r="B112" t="s">
         <v>175</v>
       </c>
-      <c r="C112" s="3" t="s">
+      <c r="C112" t="s">
         <v>180</v>
       </c>
-      <c r="D112" s="3" t="s">
+      <c r="D112" t="s">
         <v>236</v>
       </c>
-      <c r="E112" s="3" t="s">
+      <c r="E112" t="s">
         <v>712</v>
       </c>
-      <c r="F112" s="4">
+      <c r="F112" s="2">
         <v>30503</v>
       </c>
-      <c r="G112" s="3">
+      <c r="G112">
         <v>43</v>
       </c>
-      <c r="H112" s="3" t="s">
+      <c r="H112" t="s">
         <v>30</v>
       </c>
-      <c r="I112" s="3" t="s">
+      <c r="I112" t="s">
         <v>17</v>
       </c>
-      <c r="J112" s="3">
+      <c r="J112">
         <v>977634790</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A113" s="4">
+      <c r="A113" s="2">
         <v>46227</v>
       </c>
-      <c r="B113" s="3" t="s">
+      <c r="B113" t="s">
         <v>175</v>
       </c>
-      <c r="C113" s="3" t="s">
+      <c r="C113" t="s">
         <v>180</v>
       </c>
-      <c r="D113" s="3" t="s">
+      <c r="D113" t="s">
         <v>234</v>
       </c>
-      <c r="E113" s="3" t="s">
+      <c r="E113" t="s">
         <v>235</v>
       </c>
-      <c r="F113" s="4">
+      <c r="F113" s="2">
         <v>37328</v>
       </c>
-      <c r="G113" s="3">
+      <c r="G113">
         <v>24</v>
       </c>
-      <c r="H113" s="3" t="s">
+      <c r="H113" t="s">
         <v>30</v>
       </c>
-      <c r="I113" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J113" s="3">
+      <c r="I113" t="s">
+        <v>9</v>
+      </c>
+      <c r="J113">
         <v>947335085</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A114" s="4">
+      <c r="A114" s="2">
         <v>46227</v>
       </c>
-      <c r="B114" s="3" t="s">
+      <c r="B114" t="s">
         <v>175</v>
       </c>
-      <c r="C114" s="3" t="s">
+      <c r="C114" t="s">
         <v>180</v>
       </c>
-      <c r="D114" s="3" t="s">
+      <c r="D114" t="s">
         <v>444</v>
       </c>
-      <c r="E114" s="3" t="s">
+      <c r="E114" t="s">
         <v>233</v>
       </c>
-      <c r="F114" s="4">
+      <c r="F114" s="2">
         <v>35094</v>
       </c>
-      <c r="G114" s="3">
+      <c r="G114">
         <v>30</v>
       </c>
-      <c r="H114" s="3" t="s">
+      <c r="H114" t="s">
         <v>30</v>
       </c>
-      <c r="I114" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J114" s="3">
+      <c r="I114" t="s">
+        <v>9</v>
+      </c>
+      <c r="J114">
         <v>921718673</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A115" s="4">
+      <c r="A115" s="2">
         <v>46227</v>
       </c>
-      <c r="B115" s="3" t="s">
+      <c r="B115" t="s">
         <v>175</v>
       </c>
-      <c r="C115" s="3" t="s">
+      <c r="C115" t="s">
         <v>180</v>
       </c>
-      <c r="D115" s="3" t="s">
+      <c r="D115" t="s">
         <v>445</v>
       </c>
-      <c r="E115" s="3" t="s">
+      <c r="E115" t="s">
         <v>713</v>
       </c>
-      <c r="F115" s="4">
+      <c r="F115" s="2">
         <v>34047</v>
       </c>
-      <c r="G115" s="3">
+      <c r="G115">
         <v>33</v>
       </c>
-      <c r="H115" s="3" t="s">
+      <c r="H115" t="s">
         <v>30</v>
       </c>
-      <c r="I115" s="3" t="s">
+      <c r="I115" t="s">
         <v>17</v>
       </c>
-      <c r="J115" s="3">
+      <c r="J115">
         <v>929474181</v>
       </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A116" s="4">
+      <c r="A116" s="2">
         <v>46227</v>
       </c>
-      <c r="B116" s="3" t="s">
+      <c r="B116" t="s">
         <v>175</v>
       </c>
-      <c r="C116" s="3" t="s">
+      <c r="C116" t="s">
         <v>180</v>
       </c>
-      <c r="D116" s="3" t="s">
+      <c r="D116" t="s">
         <v>446</v>
       </c>
-      <c r="E116" s="3" t="s">
+      <c r="E116" t="s">
         <v>714</v>
       </c>
-      <c r="F116" s="4">
+      <c r="F116" s="2">
         <v>34826</v>
       </c>
-      <c r="G116" s="3">
+      <c r="G116">
         <v>31</v>
       </c>
-      <c r="H116" s="3" t="s">
+      <c r="H116" t="s">
         <v>30</v>
       </c>
-      <c r="I116" s="3" t="s">
+      <c r="I116" t="s">
         <v>17</v>
       </c>
-      <c r="J116" s="3">
+      <c r="J116">
         <v>994900523</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A117" s="4">
+      <c r="A117" s="2">
         <v>46227</v>
       </c>
-      <c r="B117" s="3" t="s">
+      <c r="B117" t="s">
         <v>175</v>
       </c>
-      <c r="C117" s="3" t="s">
+      <c r="C117" t="s">
         <v>180</v>
       </c>
-      <c r="D117" s="3" t="s">
+      <c r="D117" t="s">
         <v>240</v>
       </c>
-      <c r="E117" s="3" t="s">
+      <c r="E117" t="s">
         <v>241</v>
       </c>
-      <c r="F117" s="4">
+      <c r="F117" s="2">
         <v>33734</v>
       </c>
-      <c r="G117" s="3">
+      <c r="G117">
         <v>34</v>
       </c>
-      <c r="H117" s="3" t="s">
+      <c r="H117" t="s">
         <v>30</v>
       </c>
-      <c r="I117" s="3" t="s">
+      <c r="I117" t="s">
         <v>17</v>
       </c>
-      <c r="J117" s="3">
+      <c r="J117">
         <v>921098389</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A118" s="4">
+      <c r="A118" s="2">
         <v>46227</v>
       </c>
-      <c r="B118" s="3" t="s">
+      <c r="B118" t="s">
         <v>175</v>
       </c>
-      <c r="C118" s="3" t="s">
+      <c r="C118" t="s">
         <v>180</v>
       </c>
-      <c r="D118" s="3" t="s">
+      <c r="D118" t="s">
         <v>242</v>
       </c>
-      <c r="E118" s="3" t="s">
+      <c r="E118" t="s">
         <v>243</v>
       </c>
-      <c r="F118" s="4">
+      <c r="F118" s="2">
         <v>37154</v>
       </c>
-      <c r="G118" s="3">
+      <c r="G118">
         <v>24</v>
       </c>
-      <c r="H118" s="3" t="s">
+      <c r="H118" t="s">
         <v>30</v>
       </c>
-      <c r="I118" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J118" s="3">
+      <c r="I118" t="s">
+        <v>9</v>
+      </c>
+      <c r="J118">
         <v>925308991</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A119" s="4">
+      <c r="A119" s="2">
         <v>46227</v>
       </c>
-      <c r="B119" s="3" t="s">
+      <c r="B119" t="s">
         <v>175</v>
       </c>
-      <c r="C119" s="3" t="s">
+      <c r="C119" t="s">
         <v>180</v>
       </c>
-      <c r="D119" s="3" t="s">
+      <c r="D119" t="s">
         <v>246</v>
       </c>
-      <c r="E119" s="3" t="s">
+      <c r="E119" t="s">
         <v>715</v>
       </c>
-      <c r="F119" s="4">
+      <c r="F119" s="2">
         <v>32518</v>
       </c>
-      <c r="G119" s="3">
+      <c r="G119">
         <v>37</v>
       </c>
-      <c r="H119" s="3" t="s">
+      <c r="H119" t="s">
         <v>245</v>
       </c>
-      <c r="I119" s="3" t="s">
+      <c r="I119" t="s">
         <v>17</v>
       </c>
-      <c r="J119" s="3">
+      <c r="J119">
         <v>931645806</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A120" s="4">
+      <c r="A120" s="2">
         <v>46253</v>
       </c>
-      <c r="B120" s="3" t="s">
+      <c r="B120" t="s">
         <v>181</v>
       </c>
-      <c r="C120" s="3" t="s">
+      <c r="C120" t="s">
         <v>182</v>
       </c>
-      <c r="D120" s="3" t="s">
+      <c r="D120" t="s">
         <v>447</v>
       </c>
-      <c r="E120" s="3" t="s">
+      <c r="E120" t="s">
         <v>716</v>
       </c>
-      <c r="F120" s="4">
+      <c r="F120" s="2">
         <v>31951</v>
       </c>
-      <c r="G120" s="3">
+      <c r="G120">
         <v>39</v>
       </c>
-      <c r="H120" s="3" t="s">
+      <c r="H120" t="s">
         <v>343</v>
       </c>
-      <c r="I120" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J120" s="3">
+      <c r="I120" t="s">
+        <v>9</v>
+      </c>
+      <c r="J120">
         <v>992876129</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A121" s="4">
+      <c r="A121" s="2">
         <v>46253</v>
       </c>
-      <c r="B121" s="3" t="s">
+      <c r="B121" t="s">
         <v>181</v>
       </c>
-      <c r="C121" s="3" t="s">
+      <c r="C121" t="s">
         <v>182</v>
       </c>
-      <c r="D121" s="3" t="s">
+      <c r="D121" t="s">
         <v>448</v>
       </c>
-      <c r="E121" s="3" t="s">
+      <c r="E121" t="s">
         <v>717</v>
       </c>
-      <c r="F121" s="4">
+      <c r="F121" s="2">
         <v>30638</v>
       </c>
-      <c r="G121" s="3">
+      <c r="G121">
         <v>42</v>
       </c>
-      <c r="H121" s="3" t="s">
+      <c r="H121" t="s">
         <v>343</v>
       </c>
-      <c r="I121" s="3" t="s">
+      <c r="I121" t="s">
         <v>17</v>
       </c>
-      <c r="J121" s="3">
+      <c r="J121">
         <v>946302041</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A122" s="4">
+      <c r="A122" s="2">
         <v>46253</v>
       </c>
-      <c r="B122" s="3" t="s">
+      <c r="B122" t="s">
         <v>181</v>
       </c>
-      <c r="C122" s="3" t="s">
+      <c r="C122" t="s">
         <v>182</v>
       </c>
-      <c r="D122" s="3" t="s">
+      <c r="D122" t="s">
         <v>449</v>
       </c>
-      <c r="E122" s="3" t="s">
+      <c r="E122" t="s">
         <v>718</v>
       </c>
-      <c r="F122" s="4">
+      <c r="F122" s="2">
         <v>29840</v>
       </c>
-      <c r="G122" s="3">
+      <c r="G122">
         <v>45</v>
       </c>
-      <c r="H122" s="3" t="s">
+      <c r="H122" t="s">
         <v>90</v>
       </c>
-      <c r="I122" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J122" s="3">
+      <c r="I122" t="s">
+        <v>9</v>
+      </c>
+      <c r="J122">
         <v>993498995</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A123" s="4">
+      <c r="A123" s="2">
         <v>46253</v>
       </c>
-      <c r="B123" s="3" t="s">
+      <c r="B123" t="s">
         <v>181</v>
       </c>
-      <c r="C123" s="3" t="s">
+      <c r="C123" t="s">
         <v>182</v>
       </c>
-      <c r="D123" s="3" t="s">
+      <c r="D123" t="s">
         <v>450</v>
       </c>
-      <c r="E123" s="3" t="s">
+      <c r="E123" t="s">
         <v>719</v>
       </c>
-      <c r="F123" s="4">
+      <c r="F123" s="2">
         <v>24274</v>
       </c>
-      <c r="G123" s="3">
+      <c r="G123">
         <v>60</v>
       </c>
-      <c r="H123" s="3" t="s">
+      <c r="H123" t="s">
         <v>196</v>
       </c>
-      <c r="I123" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J123" s="3">
+      <c r="I123" t="s">
+        <v>9</v>
+      </c>
+      <c r="J123">
         <v>961716260</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A124" s="4">
+      <c r="A124" s="2">
         <v>46253</v>
       </c>
-      <c r="B124" s="3" t="s">
+      <c r="B124" t="s">
         <v>181</v>
       </c>
-      <c r="C124" s="3" t="s">
+      <c r="C124" t="s">
         <v>182</v>
       </c>
-      <c r="D124" s="3" t="s">
+      <c r="D124" t="s">
         <v>451</v>
       </c>
-      <c r="E124" s="3" t="s">
+      <c r="E124" t="s">
         <v>720</v>
       </c>
-      <c r="F124" s="4">
+      <c r="F124" s="2">
         <v>27433</v>
       </c>
-      <c r="G124" s="3">
+      <c r="G124">
         <v>51</v>
       </c>
-      <c r="H124" s="3" t="s">
+      <c r="H124" t="s">
         <v>97</v>
       </c>
-      <c r="I124" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J124" s="3">
+      <c r="I124" t="s">
+        <v>9</v>
+      </c>
+      <c r="J124">
         <v>969599570</v>
       </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A125" s="4">
+      <c r="A125" s="2">
         <v>46253</v>
       </c>
-      <c r="B125" s="3" t="s">
+      <c r="B125" t="s">
         <v>181</v>
       </c>
-      <c r="C125" s="3" t="s">
+      <c r="C125" t="s">
         <v>182</v>
       </c>
-      <c r="D125" s="3" t="s">
+      <c r="D125" t="s">
         <v>452</v>
       </c>
-      <c r="E125" s="3" t="s">
+      <c r="E125" t="s">
         <v>721</v>
       </c>
-      <c r="F125" s="4">
+      <c r="F125" s="2">
         <v>25981</v>
       </c>
-      <c r="G125" s="3">
+      <c r="G125">
         <v>55</v>
       </c>
-      <c r="H125" s="3" t="s">
+      <c r="H125" t="s">
         <v>196</v>
       </c>
-      <c r="I125" s="3" t="s">
+      <c r="I125" t="s">
         <v>17</v>
       </c>
-      <c r="J125" s="3">
+      <c r="J125">
         <v>980306363</v>
       </c>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A126" s="4">
+      <c r="A126" s="2">
         <v>46253</v>
       </c>
-      <c r="B126" s="3" t="s">
+      <c r="B126" t="s">
         <v>181</v>
       </c>
-      <c r="C126" s="3" t="s">
+      <c r="C126" t="s">
         <v>182</v>
       </c>
-      <c r="D126" s="3" t="s">
+      <c r="D126" t="s">
         <v>453</v>
       </c>
-      <c r="E126" s="3" t="s">
+      <c r="E126" t="s">
         <v>722</v>
       </c>
-      <c r="F126" s="4">
+      <c r="F126" s="2">
         <v>22676</v>
       </c>
-      <c r="G126" s="3">
+      <c r="G126">
         <v>64</v>
       </c>
-      <c r="H126" s="3" t="s">
+      <c r="H126" t="s">
         <v>38</v>
       </c>
-      <c r="I126" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J126" s="3">
+      <c r="I126" t="s">
+        <v>9</v>
+      </c>
+      <c r="J126">
         <v>980916551</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A127" s="4">
+      <c r="A127" s="2">
         <v>46253</v>
       </c>
-      <c r="B127" s="3" t="s">
+      <c r="B127" t="s">
         <v>181</v>
       </c>
-      <c r="C127" s="3" t="s">
+      <c r="C127" t="s">
         <v>182</v>
       </c>
-      <c r="D127" s="3" t="s">
+      <c r="D127" t="s">
         <v>454</v>
       </c>
-      <c r="E127" s="3" t="s">
+      <c r="E127" t="s">
         <v>723</v>
       </c>
-      <c r="F127" s="4">
+      <c r="F127" s="2">
         <v>29593</v>
       </c>
-      <c r="G127" s="3">
+      <c r="G127">
         <v>45</v>
       </c>
-      <c r="H127" s="3" t="s">
+      <c r="H127" t="s">
         <v>13</v>
       </c>
-      <c r="I127" s="3" t="s">
+      <c r="I127" t="s">
         <v>17</v>
       </c>
-      <c r="J127" s="3">
+      <c r="J127">
         <v>987782426</v>
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A128" s="4">
+      <c r="A128" s="2">
         <v>46253</v>
       </c>
-      <c r="B128" s="3" t="s">
+      <c r="B128" t="s">
         <v>181</v>
       </c>
-      <c r="C128" s="3" t="s">
+      <c r="C128" t="s">
         <v>182</v>
       </c>
-      <c r="D128" s="3" t="s">
+      <c r="D128" t="s">
         <v>455</v>
       </c>
-      <c r="E128" s="3" t="s">
+      <c r="E128" t="s">
         <v>724</v>
       </c>
-      <c r="F128" s="4">
+      <c r="F128" s="2">
         <v>29587</v>
       </c>
-      <c r="G128" s="3">
+      <c r="G128">
         <v>45</v>
       </c>
-      <c r="H128" s="3" t="s">
+      <c r="H128" t="s">
         <v>346</v>
       </c>
-      <c r="I128" s="3" t="s">
+      <c r="I128" t="s">
         <v>17</v>
       </c>
-      <c r="J128" s="3">
+      <c r="J128">
         <v>997887227</v>
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A129" s="4">
+      <c r="A129" s="2">
         <v>46253</v>
       </c>
-      <c r="B129" s="3" t="s">
+      <c r="B129" t="s">
         <v>181</v>
       </c>
-      <c r="C129" s="3" t="s">
+      <c r="C129" t="s">
         <v>182</v>
       </c>
-      <c r="D129" s="3" t="s">
+      <c r="D129" t="s">
         <v>456</v>
       </c>
-      <c r="E129" s="3" t="s">
+      <c r="E129" t="s">
         <v>725</v>
       </c>
-      <c r="F129" s="4">
+      <c r="F129" s="2">
         <v>29686</v>
       </c>
-      <c r="G129" s="3">
+      <c r="G129">
         <v>45</v>
       </c>
-      <c r="H129" s="3" t="s">
+      <c r="H129" t="s">
         <v>346</v>
       </c>
-      <c r="I129" s="3" t="s">
+      <c r="I129" t="s">
         <v>17</v>
       </c>
-      <c r="J129" s="3">
+      <c r="J129">
         <v>915950866</v>
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A130" s="4">
+      <c r="A130" s="2">
         <v>46253</v>
       </c>
-      <c r="B130" s="3" t="s">
+      <c r="B130" t="s">
         <v>181</v>
       </c>
-      <c r="C130" s="3" t="s">
+      <c r="C130" t="s">
         <v>182</v>
       </c>
-      <c r="D130" s="3" t="s">
+      <c r="D130" t="s">
         <v>457</v>
       </c>
-      <c r="E130" s="3" t="s">
+      <c r="E130" t="s">
         <v>726</v>
       </c>
-      <c r="F130" s="4">
+      <c r="F130" s="2">
         <v>33008</v>
       </c>
-      <c r="G130" s="3">
+      <c r="G130">
         <v>36</v>
       </c>
-      <c r="H130" s="3" t="s">
+      <c r="H130" t="s">
         <v>13</v>
       </c>
-      <c r="I130" s="3" t="s">
+      <c r="I130" t="s">
         <v>17</v>
       </c>
-      <c r="J130" s="3">
+      <c r="J130">
         <v>979381574</v>
       </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A131" s="4">
+      <c r="A131" s="2">
         <v>46253</v>
       </c>
-      <c r="B131" s="3" t="s">
+      <c r="B131" t="s">
         <v>181</v>
       </c>
-      <c r="C131" s="3" t="s">
+      <c r="C131" t="s">
         <v>182</v>
       </c>
-      <c r="D131" s="3" t="s">
+      <c r="D131" t="s">
         <v>458</v>
       </c>
-      <c r="E131" s="3" t="s">
+      <c r="E131" t="s">
         <v>727</v>
       </c>
-      <c r="F131" s="4">
+      <c r="F131" s="2">
         <v>31416</v>
       </c>
-      <c r="G131" s="3">
+      <c r="G131">
         <v>40</v>
       </c>
-      <c r="H131" s="3" t="s">
+      <c r="H131" t="s">
         <v>343</v>
       </c>
-      <c r="I131" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J131" s="3">
+      <c r="I131" t="s">
+        <v>9</v>
+      </c>
+      <c r="J131">
         <v>942872795</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A132" s="4">
+      <c r="A132" s="2">
         <v>46253</v>
       </c>
-      <c r="B132" s="3" t="s">
+      <c r="B132" t="s">
         <v>181</v>
       </c>
-      <c r="C132" s="3" t="s">
+      <c r="C132" t="s">
         <v>182</v>
       </c>
-      <c r="D132" s="3" t="s">
+      <c r="D132" t="s">
         <v>459</v>
       </c>
-      <c r="E132" s="3" t="s">
+      <c r="E132" t="s">
         <v>728</v>
       </c>
-      <c r="F132" s="4">
+      <c r="F132" s="2">
         <v>27631</v>
       </c>
-      <c r="G132" s="3">
+      <c r="G132">
         <v>51</v>
       </c>
-      <c r="H132" s="3" t="s">
+      <c r="H132" t="s">
         <v>38</v>
       </c>
-      <c r="I132" s="3" t="s">
+      <c r="I132" t="s">
         <v>17</v>
       </c>
-      <c r="J132" s="3">
+      <c r="J132">
         <v>987743833</v>
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A133" s="4">
+      <c r="A133" s="2">
         <v>46253</v>
       </c>
-      <c r="B133" s="3" t="s">
+      <c r="B133" t="s">
         <v>181</v>
       </c>
-      <c r="C133" s="3" t="s">
+      <c r="C133" t="s">
         <v>182</v>
       </c>
-      <c r="D133" s="3" t="s">
+      <c r="D133" t="s">
         <v>460</v>
       </c>
-      <c r="E133" s="3" t="s">
+      <c r="E133" t="s">
         <v>729</v>
       </c>
-      <c r="F133" s="4">
+      <c r="F133" s="2">
         <v>24948</v>
       </c>
-      <c r="G133" s="3">
+      <c r="G133">
         <v>58</v>
       </c>
-      <c r="H133" s="3" t="s">
+      <c r="H133" t="s">
         <v>343</v>
       </c>
-      <c r="I133" s="3" t="s">
+      <c r="I133" t="s">
         <v>17</v>
       </c>
-      <c r="J133" s="3">
+      <c r="J133">
         <v>989314444</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A134" s="4">
+      <c r="A134" s="2">
         <v>46253</v>
       </c>
-      <c r="B134" s="3" t="s">
+      <c r="B134" t="s">
         <v>181</v>
       </c>
-      <c r="C134" s="3" t="s">
+      <c r="C134" t="s">
         <v>182</v>
       </c>
-      <c r="D134" s="3" t="s">
+      <c r="D134" t="s">
         <v>461</v>
       </c>
-      <c r="E134" s="3" t="s">
+      <c r="E134" t="s">
         <v>730</v>
       </c>
-      <c r="F134" s="4">
+      <c r="F134" s="2">
         <v>31216</v>
       </c>
-      <c r="G134" s="3">
+      <c r="G134">
         <v>41</v>
       </c>
-      <c r="H134" s="3" t="s">
+      <c r="H134" t="s">
         <v>13</v>
       </c>
-      <c r="I134" s="3" t="s">
+      <c r="I134" t="s">
         <v>17</v>
       </c>
-      <c r="J134" s="3">
+      <c r="J134">
         <v>928665255</v>
       </c>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A135" s="4">
+      <c r="A135" s="2">
         <v>46253</v>
       </c>
-      <c r="B135" s="3" t="s">
+      <c r="B135" t="s">
         <v>181</v>
       </c>
-      <c r="C135" s="3" t="s">
+      <c r="C135" t="s">
         <v>182</v>
       </c>
-      <c r="D135" s="3" t="s">
+      <c r="D135" t="s">
         <v>247</v>
       </c>
-      <c r="E135" s="3" t="s">
+      <c r="E135" t="s">
         <v>248</v>
       </c>
-      <c r="F135" s="4">
+      <c r="F135" s="2">
         <v>21755</v>
       </c>
-      <c r="G135" s="3">
+      <c r="G135">
         <v>67</v>
       </c>
-      <c r="H135" s="3" t="s">
+      <c r="H135" t="s">
         <v>249</v>
       </c>
-      <c r="I135" s="3" t="s">
+      <c r="I135" t="s">
         <v>17</v>
       </c>
-      <c r="J135" s="3">
+      <c r="J135">
         <v>975416382</v>
       </c>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A136" s="4">
+      <c r="A136" s="2">
         <v>46253</v>
       </c>
-      <c r="B136" s="3" t="s">
+      <c r="B136" t="s">
         <v>181</v>
       </c>
-      <c r="C136" s="3" t="s">
+      <c r="C136" t="s">
         <v>182</v>
       </c>
-      <c r="D136" s="3" t="s">
+      <c r="D136" t="s">
         <v>462</v>
       </c>
-      <c r="E136" s="3" t="s">
+      <c r="E136" t="s">
         <v>731</v>
       </c>
-      <c r="F136" s="4">
+      <c r="F136" s="2">
         <v>24314</v>
       </c>
-      <c r="G136" s="3">
+      <c r="G136">
         <v>60</v>
       </c>
-      <c r="H136" s="3" t="s">
+      <c r="H136" t="s">
         <v>346</v>
       </c>
-      <c r="I136" s="3" t="s">
+      <c r="I136" t="s">
         <v>17</v>
       </c>
-      <c r="J136" s="3">
+      <c r="J136">
         <v>988095816</v>
       </c>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A137" s="4">
+      <c r="A137" s="2">
         <v>46253</v>
       </c>
-      <c r="B137" s="3" t="s">
+      <c r="B137" t="s">
         <v>181</v>
       </c>
-      <c r="C137" s="3" t="s">
+      <c r="C137" t="s">
         <v>182</v>
       </c>
-      <c r="D137" s="3" t="s">
+      <c r="D137" t="s">
         <v>463</v>
       </c>
-      <c r="E137" s="3" t="s">
+      <c r="E137" t="s">
         <v>732</v>
       </c>
-      <c r="F137" s="4">
+      <c r="F137" s="2">
         <v>25596</v>
       </c>
-      <c r="G137" s="3">
+      <c r="G137">
         <v>56</v>
       </c>
-      <c r="H137" s="3" t="s">
+      <c r="H137" t="s">
         <v>81</v>
       </c>
-      <c r="I137" s="3" t="s">
+      <c r="I137" t="s">
         <v>17</v>
       </c>
-      <c r="J137" s="3">
+      <c r="J137">
         <v>940484385</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A138" s="4">
+      <c r="A138" s="2">
         <v>46253</v>
       </c>
-      <c r="B138" s="3" t="s">
+      <c r="B138" t="s">
         <v>181</v>
       </c>
-      <c r="C138" s="3" t="s">
+      <c r="C138" t="s">
         <v>182</v>
       </c>
-      <c r="D138" s="3" t="s">
+      <c r="D138" t="s">
         <v>464</v>
       </c>
-      <c r="E138" s="3" t="s">
+      <c r="E138" t="s">
         <v>733</v>
       </c>
-      <c r="F138" s="4">
+      <c r="F138" s="2">
         <v>34150</v>
       </c>
-      <c r="G138" s="3">
+      <c r="G138">
         <v>33</v>
       </c>
-      <c r="H138" s="3" t="s">
+      <c r="H138" t="s">
         <v>346</v>
       </c>
-      <c r="I138" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J138" s="3">
+      <c r="I138" t="s">
+        <v>9</v>
+      </c>
+      <c r="J138">
         <v>924449125</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A139" s="4">
+      <c r="A139" s="2">
         <v>46253</v>
       </c>
-      <c r="B139" s="3" t="s">
+      <c r="B139" t="s">
         <v>181</v>
       </c>
-      <c r="C139" s="3" t="s">
+      <c r="C139" t="s">
         <v>182</v>
       </c>
-      <c r="D139" s="3" t="s">
+      <c r="D139" t="s">
         <v>465</v>
       </c>
-      <c r="E139" s="3" t="s">
+      <c r="E139" t="s">
         <v>734</v>
       </c>
-      <c r="F139" s="4">
+      <c r="F139" s="2">
         <v>21461</v>
       </c>
-      <c r="G139" s="3">
+      <c r="G139">
         <v>68</v>
       </c>
-      <c r="H139" s="3" t="s">
+      <c r="H139" t="s">
         <v>104</v>
       </c>
-      <c r="I139" s="3" t="s">
+      <c r="I139" t="s">
         <v>17</v>
       </c>
-      <c r="J139" s="3">
+      <c r="J139">
         <v>917988738</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A140" s="4">
+      <c r="A140" s="2">
         <v>46253</v>
       </c>
-      <c r="B140" s="3" t="s">
+      <c r="B140" t="s">
         <v>181</v>
       </c>
-      <c r="C140" s="3" t="s">
+      <c r="C140" t="s">
         <v>182</v>
       </c>
-      <c r="D140" s="3" t="s">
+      <c r="D140" t="s">
         <v>466</v>
       </c>
-      <c r="E140" s="3" t="s">
+      <c r="E140" t="s">
         <v>735</v>
       </c>
-      <c r="F140" s="4">
+      <c r="F140" s="2">
         <v>32719</v>
       </c>
-      <c r="G140" s="3">
+      <c r="G140">
         <v>37</v>
       </c>
-      <c r="H140" s="3" t="s">
+      <c r="H140" t="s">
         <v>90</v>
       </c>
-      <c r="I140" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J140" s="3">
+      <c r="I140" t="s">
+        <v>9</v>
+      </c>
+      <c r="J140">
         <v>996002731</v>
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A141" s="4">
+      <c r="A141" s="2">
         <v>46253</v>
       </c>
-      <c r="B141" s="3" t="s">
+      <c r="B141" t="s">
         <v>181</v>
       </c>
-      <c r="C141" s="3" t="s">
+      <c r="C141" t="s">
         <v>182</v>
       </c>
-      <c r="D141" s="3" t="s">
+      <c r="D141" t="s">
         <v>467</v>
       </c>
-      <c r="E141" s="3" t="s">
+      <c r="E141" t="s">
         <v>736</v>
       </c>
-      <c r="F141" s="4">
+      <c r="F141" s="2">
         <v>28470</v>
       </c>
-      <c r="G141" s="3">
+      <c r="G141">
         <v>48</v>
       </c>
-      <c r="H141" s="3" t="s">
+      <c r="H141" t="s">
         <v>90</v>
       </c>
-      <c r="I141" s="3" t="s">
+      <c r="I141" t="s">
         <v>17</v>
       </c>
-      <c r="J141" s="3">
+      <c r="J141">
         <v>971604517</v>
       </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A142" s="4">
+      <c r="A142" s="2">
         <v>46253</v>
       </c>
-      <c r="B142" s="3" t="s">
+      <c r="B142" t="s">
         <v>181</v>
       </c>
-      <c r="C142" s="3" t="s">
+      <c r="C142" t="s">
         <v>182</v>
       </c>
-      <c r="D142" s="3" t="s">
+      <c r="D142" t="s">
         <v>468</v>
       </c>
-      <c r="E142" s="3" t="s">
+      <c r="E142" t="s">
         <v>737</v>
       </c>
-      <c r="F142" s="4">
+      <c r="F142" s="2">
         <v>28090</v>
       </c>
-      <c r="G142" s="3">
+      <c r="G142">
         <v>49</v>
       </c>
-      <c r="H142" s="3" t="s">
+      <c r="H142" t="s">
         <v>102</v>
       </c>
-      <c r="I142" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J142" s="3">
+      <c r="I142" t="s">
+        <v>9</v>
+      </c>
+      <c r="J142">
         <v>992753835</v>
       </c>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A143" s="4">
+      <c r="A143" s="2">
         <v>46253</v>
       </c>
-      <c r="B143" s="3" t="s">
+      <c r="B143" t="s">
         <v>181</v>
       </c>
-      <c r="C143" s="3" t="s">
+      <c r="C143" t="s">
         <v>182</v>
       </c>
-      <c r="D143" s="3" t="s">
+      <c r="D143" t="s">
         <v>250</v>
       </c>
-      <c r="E143" s="3" t="s">
+      <c r="E143" t="s">
         <v>251</v>
       </c>
-      <c r="F143" s="4">
+      <c r="F143" s="2">
         <v>33146</v>
       </c>
-      <c r="G143" s="3">
+      <c r="G143">
         <v>36</v>
       </c>
-      <c r="H143" s="3" t="s">
+      <c r="H143" t="s">
         <v>42</v>
       </c>
-      <c r="I143" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J143" s="3">
+      <c r="I143" t="s">
+        <v>9</v>
+      </c>
+      <c r="J143">
         <v>992494151</v>
       </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A144" s="4">
+      <c r="A144" s="2">
         <v>46253</v>
       </c>
-      <c r="B144" s="3" t="s">
+      <c r="B144" t="s">
         <v>181</v>
       </c>
-      <c r="C144" s="3" t="s">
+      <c r="C144" t="s">
         <v>182</v>
       </c>
-      <c r="D144" s="3" t="s">
+      <c r="D144" t="s">
         <v>469</v>
       </c>
-      <c r="E144" s="3" t="s">
+      <c r="E144" t="s">
         <v>738</v>
       </c>
-      <c r="F144" s="4">
+      <c r="F144" s="2">
         <v>32671</v>
       </c>
-      <c r="G144" s="3">
+      <c r="G144">
         <v>37</v>
       </c>
-      <c r="H144" s="3" t="s">
+      <c r="H144" t="s">
         <v>955</v>
       </c>
-      <c r="I144" s="3" t="s">
+      <c r="I144" t="s">
         <v>17</v>
       </c>
-      <c r="J144" s="3">
+      <c r="J144">
         <v>951075749</v>
       </c>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A145" s="4">
+      <c r="A145" s="2">
         <v>46253</v>
       </c>
-      <c r="B145" s="3" t="s">
+      <c r="B145" t="s">
         <v>181</v>
       </c>
-      <c r="C145" s="3" t="s">
+      <c r="C145" t="s">
         <v>182</v>
       </c>
-      <c r="D145" s="3" t="s">
+      <c r="D145" t="s">
         <v>470</v>
       </c>
-      <c r="E145" s="3" t="s">
+      <c r="E145" t="s">
         <v>739</v>
       </c>
-      <c r="F145" s="4">
+      <c r="F145" s="2">
         <v>22853</v>
       </c>
-      <c r="G145" s="3">
+      <c r="G145">
         <v>64</v>
       </c>
-      <c r="H145" s="3" t="s">
+      <c r="H145" t="s">
         <v>13</v>
       </c>
-      <c r="I145" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J145" s="3">
+      <c r="I145" t="s">
+        <v>9</v>
+      </c>
+      <c r="J145">
         <v>958328344</v>
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A146" s="4">
+      <c r="A146" s="2">
         <v>46253</v>
       </c>
-      <c r="B146" s="3" t="s">
+      <c r="B146" t="s">
         <v>181</v>
       </c>
-      <c r="C146" s="3" t="s">
+      <c r="C146" t="s">
         <v>182</v>
       </c>
-      <c r="D146" s="3" t="s">
+      <c r="D146" t="s">
         <v>471</v>
       </c>
-      <c r="E146" s="3" t="s">
+      <c r="E146" t="s">
         <v>740</v>
       </c>
-      <c r="F146" s="4">
+      <c r="F146" s="2">
         <v>20749</v>
       </c>
-      <c r="G146" s="3">
+      <c r="G146">
         <v>69</v>
       </c>
-      <c r="H146" s="3" t="s">
+      <c r="H146" t="s">
         <v>38</v>
       </c>
-      <c r="I146" s="3" t="s">
+      <c r="I146" t="s">
         <v>17</v>
       </c>
-      <c r="J146" s="3">
+      <c r="J146">
         <v>960783165</v>
       </c>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A147" s="4">
+      <c r="A147" s="2">
         <v>46253</v>
       </c>
-      <c r="B147" s="3" t="s">
+      <c r="B147" t="s">
         <v>181</v>
       </c>
-      <c r="C147" s="3" t="s">
+      <c r="C147" t="s">
         <v>182</v>
       </c>
-      <c r="D147" s="3" t="s">
+      <c r="D147" t="s">
         <v>472</v>
       </c>
-      <c r="E147" s="3" t="s">
+      <c r="E147" t="s">
         <v>741</v>
       </c>
-      <c r="F147" s="4">
+      <c r="F147" s="2">
         <v>22958</v>
       </c>
-      <c r="G147" s="3">
+      <c r="G147">
         <v>63</v>
       </c>
-      <c r="H147" s="3" t="s">
+      <c r="H147" t="s">
         <v>954</v>
       </c>
-      <c r="I147" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J147" s="3">
+      <c r="I147" t="s">
+        <v>9</v>
+      </c>
+      <c r="J147">
         <v>989104788</v>
       </c>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A148" s="4">
+      <c r="A148" s="2">
         <v>46253</v>
       </c>
-      <c r="B148" s="3" t="s">
+      <c r="B148" t="s">
         <v>181</v>
       </c>
-      <c r="C148" s="3" t="s">
+      <c r="C148" t="s">
         <v>182</v>
       </c>
-      <c r="D148" s="3" t="s">
+      <c r="D148" t="s">
         <v>473</v>
       </c>
-      <c r="E148" s="3" t="s">
+      <c r="E148" t="s">
         <v>742</v>
       </c>
-      <c r="F148" s="4">
+      <c r="F148" s="2">
         <v>30158</v>
       </c>
-      <c r="G148" s="3">
+      <c r="G148">
         <v>44</v>
       </c>
-      <c r="H148" s="3" t="s">
+      <c r="H148" t="s">
         <v>90</v>
       </c>
-      <c r="I148" s="3" t="s">
+      <c r="I148" t="s">
         <v>17</v>
       </c>
-      <c r="J148" s="3">
+      <c r="J148">
         <v>42093626</v>
       </c>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A149" s="4">
+      <c r="A149" s="2">
         <v>46253</v>
       </c>
-      <c r="B149" s="3" t="s">
+      <c r="B149" t="s">
         <v>181</v>
       </c>
-      <c r="C149" s="3" t="s">
+      <c r="C149" t="s">
         <v>182</v>
       </c>
-      <c r="D149" s="3" t="s">
+      <c r="D149" t="s">
         <v>474</v>
       </c>
-      <c r="E149" s="3" t="s">
+      <c r="E149" t="s">
         <v>743</v>
       </c>
-      <c r="F149" s="4">
+      <c r="F149" s="2">
         <v>32015</v>
       </c>
-      <c r="G149" s="3">
+      <c r="G149">
         <v>39</v>
       </c>
-      <c r="H149" s="3" t="s">
+      <c r="H149" t="s">
         <v>343</v>
       </c>
-      <c r="I149" s="3" t="s">
+      <c r="I149" t="s">
         <v>17</v>
       </c>
-      <c r="J149" s="3">
+      <c r="J149">
         <v>984126231</v>
       </c>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A150" s="4">
+      <c r="A150" s="2">
         <v>46253</v>
       </c>
-      <c r="B150" s="3" t="s">
+      <c r="B150" t="s">
         <v>181</v>
       </c>
-      <c r="C150" s="3" t="s">
+      <c r="C150" t="s">
         <v>182</v>
       </c>
-      <c r="D150" s="3" t="s">
+      <c r="D150" t="s">
         <v>475</v>
       </c>
-      <c r="E150" s="3" t="s">
+      <c r="E150" t="s">
         <v>744</v>
       </c>
-      <c r="F150" s="4">
+      <c r="F150" s="2">
         <v>27941</v>
       </c>
-      <c r="G150" s="3">
+      <c r="G150">
         <v>50</v>
       </c>
-      <c r="H150" s="3" t="s">
+      <c r="H150" t="s">
         <v>946</v>
       </c>
-      <c r="I150" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J150" s="3">
+      <c r="I150" t="s">
+        <v>9</v>
+      </c>
+      <c r="J150">
         <v>956249623</v>
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A151" s="4">
+      <c r="A151" s="2">
         <v>46253</v>
       </c>
-      <c r="B151" s="3" t="s">
+      <c r="B151" t="s">
         <v>181</v>
       </c>
-      <c r="C151" s="3" t="s">
+      <c r="C151" t="s">
         <v>182</v>
       </c>
-      <c r="D151" s="3" t="s">
+      <c r="D151" t="s">
         <v>476</v>
       </c>
-      <c r="E151" s="3" t="s">
+      <c r="E151" t="s">
         <v>745</v>
       </c>
-      <c r="F151" s="4">
+      <c r="F151" s="2">
         <v>31250</v>
       </c>
-      <c r="G151" s="3">
+      <c r="G151">
         <v>41</v>
       </c>
-      <c r="H151" s="3" t="s">
+      <c r="H151" t="s">
         <v>249</v>
       </c>
-      <c r="I151" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J151" s="3">
+      <c r="I151" t="s">
+        <v>9</v>
+      </c>
+      <c r="J151">
         <v>976221530</v>
       </c>
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A152" s="4">
+      <c r="A152" s="2">
         <v>46253</v>
       </c>
-      <c r="B152" s="3" t="s">
+      <c r="B152" t="s">
         <v>181</v>
       </c>
-      <c r="C152" s="3" t="s">
+      <c r="C152" t="s">
         <v>182</v>
       </c>
-      <c r="D152" s="3" t="s">
+      <c r="D152" t="s">
         <v>477</v>
       </c>
-      <c r="E152" s="3" t="s">
+      <c r="E152" t="s">
         <v>746</v>
       </c>
-      <c r="F152" s="4">
+      <c r="F152" s="2">
         <v>31578</v>
       </c>
-      <c r="G152" s="3">
+      <c r="G152">
         <v>40</v>
       </c>
-      <c r="H152" s="3" t="s">
+      <c r="H152" t="s">
         <v>13</v>
       </c>
-      <c r="I152" s="3" t="s">
+      <c r="I152" t="s">
         <v>17</v>
       </c>
-      <c r="J152" s="3">
+      <c r="J152">
         <v>913977062</v>
       </c>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A153" s="4">
+      <c r="A153" s="2">
         <v>46253</v>
       </c>
-      <c r="B153" s="3" t="s">
+      <c r="B153" t="s">
         <v>181</v>
       </c>
-      <c r="C153" s="3" t="s">
+      <c r="C153" t="s">
         <v>182</v>
       </c>
-      <c r="D153" s="3" t="s">
+      <c r="D153" t="s">
         <v>478</v>
       </c>
-      <c r="E153" s="3" t="s">
+      <c r="E153" t="s">
         <v>747</v>
       </c>
-      <c r="F153" s="4">
+      <c r="F153" s="2">
         <v>25399</v>
       </c>
-      <c r="G153" s="3">
+      <c r="G153">
         <v>57</v>
       </c>
-      <c r="H153" s="3" t="s">
+      <c r="H153" t="s">
         <v>104</v>
       </c>
-      <c r="I153" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J153" s="3">
+      <c r="I153" t="s">
+        <v>9</v>
+      </c>
+      <c r="J153">
         <v>999927382</v>
       </c>
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A154" s="4">
+      <c r="A154" s="2">
         <v>46254</v>
       </c>
-      <c r="B154" s="3" t="s">
+      <c r="B154" t="s">
         <v>181</v>
       </c>
-      <c r="C154" s="3" t="s">
+      <c r="C154" t="s">
         <v>183</v>
       </c>
-      <c r="D154" s="3" t="s">
+      <c r="D154" t="s">
         <v>252</v>
       </c>
-      <c r="E154" s="3" t="s">
+      <c r="E154" t="s">
         <v>253</v>
       </c>
-      <c r="F154" s="4">
+      <c r="F154" s="2">
         <v>37938</v>
       </c>
-      <c r="G154" s="3">
+      <c r="G154">
         <v>22</v>
       </c>
-      <c r="H154" s="3" t="s">
+      <c r="H154" t="s">
         <v>38</v>
       </c>
-      <c r="I154" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J154" s="3">
+      <c r="I154" t="s">
+        <v>9</v>
+      </c>
+      <c r="J154">
         <v>950582866</v>
       </c>
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A155" s="4">
+      <c r="A155" s="2">
         <v>46254</v>
       </c>
-      <c r="B155" s="3" t="s">
+      <c r="B155" t="s">
         <v>181</v>
       </c>
-      <c r="C155" s="3" t="s">
+      <c r="C155" t="s">
         <v>183</v>
       </c>
-      <c r="D155" s="3" t="s">
+      <c r="D155" t="s">
         <v>254</v>
       </c>
-      <c r="E155" s="3" t="s">
+      <c r="E155" t="s">
         <v>255</v>
       </c>
-      <c r="F155" s="4">
+      <c r="F155" s="2">
         <v>37933</v>
       </c>
-      <c r="G155" s="3">
+      <c r="G155">
         <v>22</v>
       </c>
-      <c r="H155" s="3" t="s">
+      <c r="H155" t="s">
         <v>256</v>
       </c>
-      <c r="I155" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J155" s="3">
+      <c r="I155" t="s">
+        <v>9</v>
+      </c>
+      <c r="J155">
         <v>979620817</v>
       </c>
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A156" s="4">
+      <c r="A156" s="2">
         <v>46254</v>
       </c>
-      <c r="B156" s="3" t="s">
+      <c r="B156" t="s">
         <v>181</v>
       </c>
-      <c r="C156" s="3" t="s">
+      <c r="C156" t="s">
         <v>183</v>
       </c>
-      <c r="D156" s="3" t="s">
+      <c r="D156" t="s">
         <v>479</v>
       </c>
-      <c r="E156" s="3" t="s">
+      <c r="E156" t="s">
         <v>748</v>
       </c>
-      <c r="F156" s="4">
+      <c r="F156" s="2">
         <v>36184</v>
       </c>
-      <c r="G156" s="3">
+      <c r="G156">
         <v>27</v>
       </c>
-      <c r="H156" s="3" t="s">
+      <c r="H156" t="s">
         <v>45</v>
       </c>
-      <c r="I156" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J156" s="3">
+      <c r="I156" t="s">
+        <v>9</v>
+      </c>
+      <c r="J156">
         <v>927858702</v>
       </c>
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A157" s="4">
+      <c r="A157" s="2">
         <v>46254</v>
       </c>
-      <c r="B157" s="3" t="s">
+      <c r="B157" t="s">
         <v>181</v>
       </c>
-      <c r="C157" s="3" t="s">
+      <c r="C157" t="s">
         <v>183</v>
       </c>
-      <c r="D157" s="3">
+      <c r="D157">
         <v>76916146</v>
       </c>
-      <c r="E157" s="3" t="s">
+      <c r="E157" t="s">
         <v>749</v>
       </c>
-      <c r="F157" s="4">
+      <c r="F157" s="2">
         <v>35361</v>
       </c>
-      <c r="G157" s="3">
+      <c r="G157">
         <v>29</v>
       </c>
-      <c r="H157" s="3" t="s">
+      <c r="H157" t="s">
         <v>38</v>
       </c>
-      <c r="I157" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J157" s="3"/>
+      <c r="I157" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A158" s="4">
+      <c r="A158" s="2">
         <v>46254</v>
       </c>
-      <c r="B158" s="3" t="s">
+      <c r="B158" t="s">
         <v>181</v>
       </c>
-      <c r="C158" s="3" t="s">
+      <c r="C158" t="s">
         <v>183</v>
       </c>
-      <c r="D158" s="3" t="s">
+      <c r="D158" t="s">
         <v>480</v>
       </c>
-      <c r="E158" s="3" t="s">
+      <c r="E158" t="s">
         <v>750</v>
       </c>
-      <c r="F158" s="4">
+      <c r="F158" s="2">
         <v>31486</v>
       </c>
-      <c r="G158" s="3">
+      <c r="G158">
         <v>40</v>
       </c>
-      <c r="H158" s="3" t="s">
+      <c r="H158" t="s">
         <v>346</v>
       </c>
-      <c r="I158" s="3" t="s">
+      <c r="I158" t="s">
         <v>17</v>
       </c>
-      <c r="J158" s="3">
+      <c r="J158">
         <v>966149257</v>
       </c>
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A159" s="4">
+      <c r="A159" s="2">
         <v>46254</v>
       </c>
-      <c r="B159" s="3" t="s">
+      <c r="B159" t="s">
         <v>181</v>
       </c>
-      <c r="C159" s="3" t="s">
+      <c r="C159" t="s">
         <v>183</v>
       </c>
-      <c r="D159" s="3" t="s">
+      <c r="D159" t="s">
         <v>481</v>
       </c>
-      <c r="E159" s="3" t="s">
+      <c r="E159" t="s">
         <v>751</v>
       </c>
-      <c r="F159" s="4">
+      <c r="F159" s="2">
         <v>27101</v>
       </c>
-      <c r="G159" s="3">
+      <c r="G159">
         <v>52</v>
       </c>
-      <c r="H159" s="3" t="s">
+      <c r="H159" t="s">
         <v>42</v>
       </c>
-      <c r="I159" s="3" t="s">
+      <c r="I159" t="s">
         <v>17</v>
       </c>
-      <c r="J159" s="3">
+      <c r="J159">
         <v>938487689</v>
       </c>
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A160" s="4">
+      <c r="A160" s="2">
         <v>46254</v>
       </c>
-      <c r="B160" s="3" t="s">
+      <c r="B160" t="s">
         <v>181</v>
       </c>
-      <c r="C160" s="3" t="s">
+      <c r="C160" t="s">
         <v>183</v>
       </c>
-      <c r="D160" s="3" t="s">
+      <c r="D160" t="s">
         <v>482</v>
       </c>
-      <c r="E160" s="3" t="s">
+      <c r="E160" t="s">
         <v>752</v>
       </c>
-      <c r="F160" s="4">
+      <c r="F160" s="2">
         <v>38091</v>
       </c>
-      <c r="G160" s="3">
+      <c r="G160">
         <v>22</v>
       </c>
-      <c r="H160" s="3" t="s">
+      <c r="H160" t="s">
         <v>38</v>
       </c>
-      <c r="I160" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J160" s="3">
+      <c r="I160" t="s">
+        <v>9</v>
+      </c>
+      <c r="J160">
         <v>994955938</v>
       </c>
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A161" s="4">
+      <c r="A161" s="2">
         <v>46254</v>
       </c>
-      <c r="B161" s="3" t="s">
+      <c r="B161" t="s">
         <v>181</v>
       </c>
-      <c r="C161" s="3" t="s">
+      <c r="C161" t="s">
         <v>183</v>
       </c>
-      <c r="D161" s="3" t="s">
+      <c r="D161" t="s">
         <v>483</v>
       </c>
-      <c r="E161" s="3" t="s">
+      <c r="E161" t="s">
         <v>753</v>
       </c>
-      <c r="F161" s="4">
+      <c r="F161" s="2">
         <v>33738</v>
       </c>
-      <c r="G161" s="3">
+      <c r="G161">
         <v>34</v>
       </c>
-      <c r="H161" s="3" t="s">
+      <c r="H161" t="s">
         <v>38</v>
       </c>
-      <c r="I161" s="3" t="s">
+      <c r="I161" t="s">
         <v>17</v>
       </c>
-      <c r="J161" s="3">
+      <c r="J161">
         <v>949214644</v>
       </c>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A162" s="4">
+      <c r="A162" s="2">
         <v>46254</v>
       </c>
-      <c r="B162" s="3" t="s">
+      <c r="B162" t="s">
         <v>181</v>
       </c>
-      <c r="C162" s="3" t="s">
+      <c r="C162" t="s">
         <v>183</v>
       </c>
-      <c r="D162" s="3" t="s">
+      <c r="D162" t="s">
         <v>484</v>
       </c>
-      <c r="E162" s="3" t="s">
+      <c r="E162" t="s">
         <v>754</v>
       </c>
-      <c r="F162" s="4">
+      <c r="F162" s="2">
         <v>36782</v>
       </c>
-      <c r="G162" s="3">
+      <c r="G162">
         <v>26</v>
       </c>
-      <c r="H162" s="3" t="s">
+      <c r="H162" t="s">
         <v>90</v>
       </c>
-      <c r="I162" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J162" s="3">
+      <c r="I162" t="s">
+        <v>9</v>
+      </c>
+      <c r="J162">
         <v>976508386</v>
       </c>
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A163" s="4">
+      <c r="A163" s="2">
         <v>46254</v>
       </c>
-      <c r="B163" s="3" t="s">
+      <c r="B163" t="s">
         <v>181</v>
       </c>
-      <c r="C163" s="3" t="s">
+      <c r="C163" t="s">
         <v>183</v>
       </c>
-      <c r="D163" s="3" t="s">
+      <c r="D163" t="s">
         <v>485</v>
       </c>
-      <c r="E163" s="3" t="s">
+      <c r="E163" t="s">
         <v>755</v>
       </c>
-      <c r="F163" s="4">
+      <c r="F163" s="2">
         <v>28856</v>
       </c>
-      <c r="G163" s="3">
+      <c r="G163">
         <v>47</v>
       </c>
-      <c r="H163" s="3" t="s">
+      <c r="H163" t="s">
         <v>16</v>
       </c>
-      <c r="I163" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J163" s="3">
+      <c r="I163" t="s">
+        <v>9</v>
+      </c>
+      <c r="J163">
         <v>932203539</v>
       </c>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A164" s="4">
+      <c r="A164" s="2">
         <v>46254</v>
       </c>
-      <c r="B164" s="3" t="s">
+      <c r="B164" t="s">
         <v>181</v>
       </c>
-      <c r="C164" s="3" t="s">
+      <c r="C164" t="s">
         <v>183</v>
       </c>
-      <c r="D164" s="3" t="s">
+      <c r="D164" t="s">
         <v>486</v>
       </c>
-      <c r="E164" s="3" t="s">
+      <c r="E164" t="s">
         <v>756</v>
       </c>
-      <c r="F164" s="4">
+      <c r="F164" s="2">
         <v>29345</v>
       </c>
-      <c r="G164" s="3">
+      <c r="G164">
         <v>46</v>
       </c>
-      <c r="H164" s="3" t="s">
+      <c r="H164" t="s">
         <v>956</v>
       </c>
-      <c r="I164" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J164" s="3">
+      <c r="I164" t="s">
+        <v>9</v>
+      </c>
+      <c r="J164">
         <v>941464361</v>
       </c>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A165" s="4">
+      <c r="A165" s="2">
         <v>46254</v>
       </c>
-      <c r="B165" s="3" t="s">
+      <c r="B165" t="s">
         <v>181</v>
       </c>
-      <c r="C165" s="3" t="s">
+      <c r="C165" t="s">
         <v>183</v>
       </c>
-      <c r="D165" s="3" t="s">
+      <c r="D165" t="s">
         <v>257</v>
       </c>
-      <c r="E165" s="3" t="s">
+      <c r="E165" t="s">
         <v>258</v>
       </c>
-      <c r="F165" s="4">
+      <c r="F165" s="2">
         <v>31529</v>
       </c>
-      <c r="G165" s="3">
+      <c r="G165">
         <v>40</v>
       </c>
-      <c r="H165" s="3" t="s">
+      <c r="H165" t="s">
         <v>16</v>
       </c>
-      <c r="I165" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J165" s="3">
+      <c r="I165" t="s">
+        <v>9</v>
+      </c>
+      <c r="J165">
         <v>959841315</v>
       </c>
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A166" s="4">
+      <c r="A166" s="2">
         <v>46254</v>
       </c>
-      <c r="B166" s="3" t="s">
+      <c r="B166" t="s">
         <v>181</v>
       </c>
-      <c r="C166" s="3" t="s">
+      <c r="C166" t="s">
         <v>183</v>
       </c>
-      <c r="D166" s="3" t="s">
+      <c r="D166" t="s">
         <v>487</v>
       </c>
-      <c r="E166" s="3" t="s">
+      <c r="E166" t="s">
         <v>757</v>
       </c>
-      <c r="F166" s="4">
+      <c r="F166" s="2">
         <v>33722</v>
       </c>
-      <c r="G166" s="3">
+      <c r="G166">
         <v>34</v>
       </c>
-      <c r="H166" s="3" t="s">
+      <c r="H166" t="s">
         <v>16</v>
       </c>
-      <c r="I166" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J166" s="3">
+      <c r="I166" t="s">
+        <v>9</v>
+      </c>
+      <c r="J166">
         <v>922630546</v>
       </c>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A167" s="4">
+      <c r="A167" s="2">
         <v>46254</v>
       </c>
-      <c r="B167" s="3" t="s">
+      <c r="B167" t="s">
         <v>181</v>
       </c>
-      <c r="C167" s="3" t="s">
+      <c r="C167" t="s">
         <v>183</v>
       </c>
-      <c r="D167" s="3" t="s">
+      <c r="D167" t="s">
         <v>488</v>
       </c>
-      <c r="E167" s="3" t="s">
+      <c r="E167" t="s">
         <v>758</v>
       </c>
-      <c r="F167" s="4">
+      <c r="F167" s="2">
         <v>35599</v>
       </c>
-      <c r="G167" s="3">
+      <c r="G167">
         <v>29</v>
       </c>
-      <c r="H167" s="3" t="s">
+      <c r="H167" t="s">
         <v>16</v>
       </c>
-      <c r="I167" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J167" s="3">
+      <c r="I167" t="s">
+        <v>9</v>
+      </c>
+      <c r="J167">
         <v>947326865</v>
       </c>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A168" s="4">
+      <c r="A168" s="2">
         <v>46254</v>
       </c>
-      <c r="B168" s="3" t="s">
+      <c r="B168" t="s">
         <v>181</v>
       </c>
-      <c r="C168" s="3" t="s">
+      <c r="C168" t="s">
         <v>183</v>
       </c>
-      <c r="D168" s="3" t="s">
+      <c r="D168" t="s">
         <v>489</v>
       </c>
-      <c r="E168" s="3" t="s">
+      <c r="E168" t="s">
         <v>759</v>
       </c>
-      <c r="F168" s="4">
+      <c r="F168" s="2">
         <v>24845</v>
       </c>
-      <c r="G168" s="3">
+      <c r="G168">
         <v>58</v>
       </c>
-      <c r="H168" s="3" t="s">
+      <c r="H168" t="s">
         <v>949</v>
       </c>
-      <c r="I168" s="3" t="s">
+      <c r="I168" t="s">
         <v>17</v>
       </c>
-      <c r="J168" s="3">
+      <c r="J168">
         <v>996652679</v>
       </c>
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A169" s="4">
+      <c r="A169" s="2">
         <v>46254</v>
       </c>
-      <c r="B169" s="3" t="s">
+      <c r="B169" t="s">
         <v>181</v>
       </c>
-      <c r="C169" s="3" t="s">
+      <c r="C169" t="s">
         <v>183</v>
       </c>
-      <c r="D169" s="3" t="s">
+      <c r="D169" t="s">
         <v>490</v>
       </c>
-      <c r="E169" s="3" t="s">
+      <c r="E169" t="s">
         <v>760</v>
       </c>
-      <c r="F169" s="4">
+      <c r="F169" s="2">
         <v>31864</v>
       </c>
-      <c r="G169" s="3">
+      <c r="G169">
         <v>39</v>
       </c>
-      <c r="H169" s="3" t="s">
+      <c r="H169" t="s">
         <v>45</v>
       </c>
-      <c r="I169" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J169" s="3">
+      <c r="I169" t="s">
+        <v>9</v>
+      </c>
+      <c r="J169">
         <v>924948622</v>
       </c>
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A170" s="4">
+      <c r="A170" s="2">
         <v>46254</v>
       </c>
-      <c r="B170" s="3" t="s">
+      <c r="B170" t="s">
         <v>181</v>
       </c>
-      <c r="C170" s="3" t="s">
+      <c r="C170" t="s">
         <v>183</v>
       </c>
-      <c r="D170" s="3" t="s">
+      <c r="D170" t="s">
         <v>491</v>
       </c>
-      <c r="E170" s="3" t="s">
+      <c r="E170" t="s">
         <v>761</v>
       </c>
-      <c r="F170" s="4">
+      <c r="F170" s="2">
         <v>32255</v>
       </c>
-      <c r="G170" s="3">
+      <c r="G170">
         <v>38</v>
       </c>
-      <c r="H170" s="3" t="s">
+      <c r="H170" t="s">
         <v>45</v>
       </c>
-      <c r="I170" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J170" s="3">
+      <c r="I170" t="s">
+        <v>9</v>
+      </c>
+      <c r="J170">
         <v>940838776</v>
       </c>
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A171" s="4">
+      <c r="A171" s="2">
         <v>46254</v>
       </c>
-      <c r="B171" s="3" t="s">
+      <c r="B171" t="s">
         <v>181</v>
       </c>
-      <c r="C171" s="3" t="s">
+      <c r="C171" t="s">
         <v>183</v>
       </c>
-      <c r="D171" s="3" t="s">
+      <c r="D171" t="s">
         <v>492</v>
       </c>
-      <c r="E171" s="3" t="s">
+      <c r="E171" t="s">
         <v>762</v>
       </c>
-      <c r="F171" s="4">
+      <c r="F171" s="2">
         <v>30536</v>
       </c>
-      <c r="G171" s="3">
+      <c r="G171">
         <v>43</v>
       </c>
-      <c r="H171" s="3" t="s">
+      <c r="H171" t="s">
         <v>346</v>
       </c>
-      <c r="I171" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J171" s="3">
+      <c r="I171" t="s">
+        <v>9</v>
+      </c>
+      <c r="J171">
         <v>966468928</v>
       </c>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A172" s="4">
+      <c r="A172" s="2">
         <v>46254</v>
       </c>
-      <c r="B172" s="3" t="s">
+      <c r="B172" t="s">
         <v>181</v>
       </c>
-      <c r="C172" s="3" t="s">
+      <c r="C172" t="s">
         <v>183</v>
       </c>
-      <c r="D172" s="3" t="s">
+      <c r="D172" t="s">
         <v>493</v>
       </c>
-      <c r="E172" s="3" t="s">
+      <c r="E172" t="s">
         <v>763</v>
       </c>
-      <c r="F172" s="4">
+      <c r="F172" s="2">
         <v>31771</v>
       </c>
-      <c r="G172" s="3">
+      <c r="G172">
         <v>39</v>
       </c>
-      <c r="H172" s="3" t="s">
+      <c r="H172" t="s">
         <v>957</v>
       </c>
-      <c r="I172" s="3" t="s">
+      <c r="I172" t="s">
         <v>17</v>
       </c>
-      <c r="J172" s="3">
+      <c r="J172">
         <v>973837354</v>
       </c>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A173" s="4">
+      <c r="A173" s="2">
         <v>46254</v>
       </c>
-      <c r="B173" s="3" t="s">
+      <c r="B173" t="s">
         <v>181</v>
       </c>
-      <c r="C173" s="3" t="s">
+      <c r="C173" t="s">
         <v>183</v>
       </c>
-      <c r="D173" s="3" t="s">
+      <c r="D173" t="s">
         <v>259</v>
       </c>
-      <c r="E173" s="3" t="s">
+      <c r="E173" t="s">
         <v>260</v>
       </c>
-      <c r="F173" s="4">
+      <c r="F173" s="2">
         <v>36277</v>
       </c>
-      <c r="G173" s="3">
+      <c r="G173">
         <v>27</v>
       </c>
-      <c r="H173" s="3" t="s">
+      <c r="H173" t="s">
         <v>261</v>
       </c>
-      <c r="I173" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J173" s="3">
+      <c r="I173" t="s">
+        <v>9</v>
+      </c>
+      <c r="J173">
         <v>969691471</v>
       </c>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A174" s="4">
+      <c r="A174" s="2">
         <v>46254</v>
       </c>
-      <c r="B174" s="3" t="s">
+      <c r="B174" t="s">
         <v>181</v>
       </c>
-      <c r="C174" s="3" t="s">
+      <c r="C174" t="s">
         <v>183</v>
       </c>
-      <c r="D174" s="3" t="s">
+      <c r="D174" t="s">
         <v>494</v>
       </c>
-      <c r="E174" s="3" t="s">
+      <c r="E174" t="s">
         <v>764</v>
       </c>
-      <c r="F174" s="4">
+      <c r="F174" s="2">
         <v>36929</v>
       </c>
-      <c r="G174" s="3">
+      <c r="G174">
         <v>25</v>
       </c>
-      <c r="H174" s="3" t="s">
+      <c r="H174" t="s">
         <v>20</v>
       </c>
-      <c r="I174" s="3" t="s">
+      <c r="I174" t="s">
         <v>17</v>
       </c>
-      <c r="J174" s="3">
+      <c r="J174">
         <v>990651995</v>
       </c>
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A175" s="4">
+      <c r="A175" s="2">
         <v>46258</v>
       </c>
-      <c r="B175" s="3" t="s">
+      <c r="B175" t="s">
         <v>181</v>
       </c>
-      <c r="C175" s="3" t="s">
+      <c r="C175" t="s">
         <v>184</v>
       </c>
-      <c r="D175" s="3" t="s">
+      <c r="D175" t="s">
         <v>495</v>
       </c>
-      <c r="E175" s="3" t="s">
+      <c r="E175" t="s">
         <v>765</v>
       </c>
-      <c r="F175" s="4">
+      <c r="F175" s="2">
         <v>38260</v>
       </c>
-      <c r="G175" s="3">
+      <c r="G175">
         <v>21</v>
       </c>
-      <c r="H175" s="3" t="s">
+      <c r="H175" t="s">
         <v>42</v>
       </c>
-      <c r="I175" s="3" t="s">
+      <c r="I175" t="s">
         <v>17</v>
       </c>
-      <c r="J175" s="3">
+      <c r="J175">
         <v>912237580</v>
       </c>
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A176" s="4">
+      <c r="A176" s="2">
         <v>46258</v>
       </c>
-      <c r="B176" s="3" t="s">
+      <c r="B176" t="s">
         <v>181</v>
       </c>
-      <c r="C176" s="3" t="s">
+      <c r="C176" t="s">
         <v>184</v>
       </c>
-      <c r="D176" s="3" t="s">
+      <c r="D176" t="s">
         <v>496</v>
       </c>
-      <c r="E176" s="3" t="s">
+      <c r="E176" t="s">
         <v>766</v>
       </c>
-      <c r="F176" s="4">
+      <c r="F176" s="2">
         <v>32111</v>
       </c>
-      <c r="G176" s="3">
+      <c r="G176">
         <v>38</v>
       </c>
-      <c r="H176" s="3" t="s">
+      <c r="H176" t="s">
         <v>162</v>
       </c>
-      <c r="I176" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J176" s="3">
+      <c r="I176" t="s">
+        <v>9</v>
+      </c>
+      <c r="J176">
         <v>924449918</v>
       </c>
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A177" s="4">
+      <c r="A177" s="2">
         <v>46258</v>
       </c>
-      <c r="B177" s="3" t="s">
+      <c r="B177" t="s">
         <v>181</v>
       </c>
-      <c r="C177" s="3" t="s">
+      <c r="C177" t="s">
         <v>184</v>
       </c>
-      <c r="D177" s="3" t="s">
+      <c r="D177" t="s">
         <v>497</v>
       </c>
-      <c r="E177" s="3" t="s">
+      <c r="E177" t="s">
         <v>767</v>
       </c>
-      <c r="F177" s="4">
+      <c r="F177" s="2">
         <v>38173</v>
       </c>
-      <c r="G177" s="3">
+      <c r="G177">
         <v>22</v>
       </c>
-      <c r="H177" s="3" t="s">
+      <c r="H177" t="s">
         <v>137</v>
       </c>
-      <c r="I177" s="3" t="s">
+      <c r="I177" t="s">
         <v>17</v>
       </c>
-      <c r="J177" s="3">
+      <c r="J177">
         <v>900543342</v>
       </c>
     </row>
@@ -19349,7 +19344,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
         <v>46227</v>
       </c>
@@ -19371,8 +19366,11 @@
       <c r="J49" s="1">
         <v>50</v>
       </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K49" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
         <v>46227</v>
       </c>
@@ -19400,8 +19398,11 @@
       <c r="J50" s="1">
         <v>99</v>
       </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K50" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
         <v>46227</v>
       </c>
@@ -19423,8 +19424,11 @@
       <c r="J51" s="1">
         <v>50</v>
       </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K51" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
         <v>46227</v>
       </c>
@@ -19452,8 +19456,11 @@
       <c r="J52" s="1">
         <v>99</v>
       </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K52" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
         <v>46227</v>
       </c>
@@ -19475,8 +19482,11 @@
       <c r="J53" s="1">
         <v>50</v>
       </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K53" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
         <v>46227</v>
       </c>
@@ -19504,8 +19514,11 @@
       <c r="J54" s="1">
         <v>199</v>
       </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K54" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
         <v>46227</v>
       </c>
@@ -19527,8 +19540,11 @@
       <c r="J55" s="1">
         <v>50</v>
       </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K55" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
         <v>46227</v>
       </c>
@@ -19556,8 +19572,11 @@
       <c r="J56" s="1">
         <v>99</v>
       </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K56" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
         <v>46227</v>
       </c>
@@ -19579,8 +19598,11 @@
       <c r="J57" s="1">
         <v>50</v>
       </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K57" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
         <v>46227</v>
       </c>
@@ -19608,8 +19630,11 @@
       <c r="J58" s="1">
         <v>299</v>
       </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K58" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" s="2">
         <v>46227</v>
       </c>
@@ -19631,8 +19656,11 @@
       <c r="J59" s="1">
         <v>50</v>
       </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K59" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
         <v>46227</v>
       </c>
@@ -19660,8 +19688,11 @@
       <c r="J60" s="1">
         <v>299</v>
       </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K60" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
         <v>46253</v>
       </c>
@@ -19680,8 +19711,11 @@
       <c r="J61" s="1">
         <v>50</v>
       </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K61" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
         <v>46253</v>
       </c>
@@ -19709,8 +19743,11 @@
       <c r="J62" s="1">
         <v>49</v>
       </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K62" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
         <v>46253</v>
       </c>
@@ -19729,8 +19766,11 @@
       <c r="J63" s="1">
         <v>50</v>
       </c>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K63" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
         <v>46253</v>
       </c>
@@ -19757,6 +19797,9 @@
       </c>
       <c r="J64" s="1">
         <v>49</v>
+      </c>
+      <c r="K64" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.3">
@@ -19804,6 +19847,9 @@
       <c r="J66" s="1">
         <v>50</v>
       </c>
+      <c r="K66" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
@@ -19833,6 +19879,9 @@
       <c r="J67" s="1">
         <v>49</v>
       </c>
+      <c r="K67" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
@@ -19856,6 +19905,9 @@
       <c r="J68" s="1">
         <v>50</v>
       </c>
+      <c r="K68" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
@@ -19960,6 +20012,9 @@
       <c r="J72" s="1">
         <v>50</v>
       </c>
+      <c r="K72" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73" s="2">
@@ -19989,6 +20044,9 @@
       <c r="J73" s="1">
         <v>199</v>
       </c>
+      <c r="K73" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74" s="2">
@@ -20012,6 +20070,9 @@
       <c r="J74" s="1">
         <v>50</v>
       </c>
+      <c r="K74" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75" s="2">
@@ -20041,6 +20102,9 @@
       <c r="J75" s="1">
         <v>199</v>
       </c>
+      <c r="K75" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76" s="2">
@@ -20064,6 +20128,9 @@
       <c r="J76" s="1">
         <v>50</v>
       </c>
+      <c r="K76" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77" s="2">
@@ -20093,6 +20160,9 @@
       <c r="J77" s="1">
         <v>199</v>
       </c>
+      <c r="K77" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78" s="2">
@@ -20168,6 +20238,9 @@
       <c r="J80" s="1">
         <v>50</v>
       </c>
+      <c r="K80" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A81" s="2">
@@ -20197,6 +20270,9 @@
       <c r="J81" s="1">
         <v>369</v>
       </c>
+      <c r="K81" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A82" s="2">
@@ -20220,6 +20296,9 @@
       <c r="J82" s="1">
         <v>50</v>
       </c>
+      <c r="K82" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A83" s="2">
@@ -20243,6 +20322,9 @@
       <c r="J83" s="1">
         <v>50</v>
       </c>
+      <c r="K83" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A84" s="2">
@@ -20266,6 +20348,9 @@
       <c r="J84" s="1">
         <v>50</v>
       </c>
+      <c r="K84" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A85" s="2">
@@ -20295,6 +20380,9 @@
       <c r="J85" s="1">
         <v>99</v>
       </c>
+      <c r="K85" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A86" s="2">
@@ -20422,6 +20510,9 @@
       <c r="J90" s="1">
         <v>50</v>
       </c>
+      <c r="K90" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A91" s="2">
@@ -20451,6 +20542,9 @@
       <c r="J91" s="1">
         <v>199</v>
       </c>
+      <c r="K91" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A92" s="2">
@@ -20474,6 +20568,9 @@
       <c r="J92" s="1">
         <v>50</v>
       </c>
+      <c r="K92" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A93" s="2">
@@ -20503,6 +20600,9 @@
       <c r="J93" s="1">
         <v>199</v>
       </c>
+      <c r="K93" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A94" s="2">
@@ -20552,6 +20652,9 @@
       <c r="J95" s="1">
         <v>50</v>
       </c>
+      <c r="K95" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A96" s="2">
@@ -20581,6 +20684,9 @@
       <c r="J96" s="1">
         <v>599</v>
       </c>
+      <c r="K96" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A97" s="2">
@@ -20604,6 +20710,9 @@
       <c r="J97" s="1">
         <v>50</v>
       </c>
+      <c r="K97" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A98" s="2">
@@ -20633,6 +20742,9 @@
       <c r="J98" s="1">
         <v>99</v>
       </c>
+      <c r="K98" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A99" s="2">
@@ -20682,6 +20794,9 @@
       <c r="J100" s="1">
         <v>70</v>
       </c>
+      <c r="K100" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A101" s="2">
@@ -20711,6 +20826,9 @@
       <c r="J101" s="1">
         <v>649</v>
       </c>
+      <c r="K101" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A102" s="2">
@@ -20734,6 +20852,9 @@
       <c r="J102" s="1">
         <v>70</v>
       </c>
+      <c r="K102" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A103" s="2">
@@ -20763,6 +20884,9 @@
       <c r="J103" s="1">
         <v>649</v>
       </c>
+      <c r="K103" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A104" s="2">
@@ -20838,6 +20962,9 @@
       <c r="J106" s="1">
         <v>50</v>
       </c>
+      <c r="K106" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A107" s="2">
@@ -20867,6 +20994,9 @@
       <c r="J107" s="1">
         <v>99</v>
       </c>
+      <c r="K107" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A108" s="2">
@@ -20890,6 +21020,9 @@
       <c r="J108" s="1">
         <v>50</v>
       </c>
+      <c r="K108" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A109" s="2">
@@ -20919,6 +21052,9 @@
       <c r="J109" s="1">
         <v>199</v>
       </c>
+      <c r="K109" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A110" s="2">
@@ -20942,6 +21078,9 @@
       <c r="J110" s="1">
         <v>70</v>
       </c>
+      <c r="K110" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A111" s="2">
@@ -20971,6 +21110,9 @@
       <c r="J111" s="1">
         <v>199</v>
       </c>
+      <c r="K111" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A112" s="2">
@@ -20994,8 +21136,11 @@
       <c r="J112" s="1">
         <v>50</v>
       </c>
-    </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K112" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A113" s="2">
         <v>46269</v>
       </c>
@@ -21023,8 +21168,11 @@
       <c r="J113" s="1">
         <v>199</v>
       </c>
-    </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K113" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A114" s="2">
         <v>46269</v>
       </c>
@@ -21046,8 +21194,11 @@
       <c r="J114" s="1">
         <v>50</v>
       </c>
-    </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K114" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A115" s="2">
         <v>46269</v>
       </c>
@@ -21075,8 +21226,11 @@
       <c r="J115" s="1">
         <v>149</v>
       </c>
-    </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K115" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A116" s="2">
         <v>46269</v>
       </c>
@@ -21098,8 +21252,11 @@
       <c r="J116" s="1">
         <v>50</v>
       </c>
-    </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K116" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A117" s="2">
         <v>46269</v>
       </c>
@@ -21127,8 +21284,11 @@
       <c r="J117" s="1">
         <v>49</v>
       </c>
-    </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K117" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A118" s="2">
         <v>46269</v>
       </c>
@@ -21150,8 +21310,11 @@
       <c r="J118" s="1">
         <v>50</v>
       </c>
-    </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K118" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A119" s="2">
         <v>46269</v>
       </c>
@@ -21179,8 +21342,11 @@
       <c r="J119" s="1">
         <v>99</v>
       </c>
-    </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K119" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A120" s="2">
         <v>46269</v>
       </c>
@@ -21202,8 +21368,11 @@
       <c r="J120" s="1">
         <v>50</v>
       </c>
-    </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K120" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A121" s="2">
         <v>46269</v>
       </c>
@@ -21231,8 +21400,11 @@
       <c r="J121" s="1">
         <v>99</v>
       </c>
-    </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K121" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A122" s="2">
         <v>46269</v>
       </c>
@@ -21254,8 +21426,11 @@
       <c r="J122" s="1">
         <v>50</v>
       </c>
-    </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K122" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A123" s="2">
         <v>46269</v>
       </c>
@@ -21283,8 +21458,11 @@
       <c r="J123" s="1">
         <v>99</v>
       </c>
-    </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K123" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A124" s="2">
         <v>46269</v>
       </c>
@@ -21306,8 +21484,11 @@
       <c r="J124" s="1">
         <v>50</v>
       </c>
-    </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K124" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A125" s="2">
         <v>46269</v>
       </c>
@@ -21335,8 +21516,11 @@
       <c r="J125" s="1">
         <v>99</v>
       </c>
-    </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K125" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A126" s="2">
         <v>46269</v>
       </c>
@@ -21358,8 +21542,11 @@
       <c r="J126" s="1">
         <v>50</v>
       </c>
-    </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K126" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A127" s="2">
         <v>46269</v>
       </c>
@@ -21387,8 +21574,11 @@
       <c r="J127" s="1">
         <v>99</v>
       </c>
-    </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K127" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A128" s="2">
         <v>46269</v>
       </c>
@@ -21410,8 +21600,11 @@
       <c r="J128" s="1">
         <v>50</v>
       </c>
-    </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K128" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A129" s="2">
         <v>46269</v>
       </c>
@@ -21439,8 +21632,11 @@
       <c r="J129" s="1">
         <v>199</v>
       </c>
-    </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K129" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A130" s="2">
         <v>46269</v>
       </c>
@@ -21462,8 +21658,11 @@
       <c r="J130" s="1">
         <v>50</v>
       </c>
-    </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K130" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A131" s="2">
         <v>46269</v>
       </c>
@@ -21491,8 +21690,11 @@
       <c r="J131" s="1">
         <v>199</v>
       </c>
-    </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K131" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A132" s="2">
         <v>46269</v>
       </c>
@@ -21514,8 +21716,11 @@
       <c r="J132" s="1">
         <v>50</v>
       </c>
-    </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K132" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A133" s="2">
         <v>46269</v>
       </c>
@@ -21543,8 +21748,11 @@
       <c r="J133" s="1">
         <v>199</v>
       </c>
-    </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K133" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A134" s="2">
         <v>46274</v>
       </c>
@@ -21566,8 +21774,11 @@
       <c r="J134" s="1">
         <v>50</v>
       </c>
-    </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K134" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A135" s="2">
         <v>46274</v>
       </c>
@@ -21595,8 +21806,11 @@
       <c r="J135" s="1">
         <v>49</v>
       </c>
-    </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K135" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A136" s="2">
         <v>46274</v>
       </c>
@@ -21618,8 +21832,11 @@
       <c r="J136" s="1">
         <v>50</v>
       </c>
-    </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K136" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A137" s="2">
         <v>46274</v>
       </c>
@@ -21647,8 +21864,11 @@
       <c r="J137" s="1">
         <v>299</v>
       </c>
-    </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K137" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A138" s="2">
         <v>46274</v>
       </c>
@@ -21670,8 +21890,11 @@
       <c r="J138" s="1">
         <v>70</v>
       </c>
-    </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K138" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A139" s="2">
         <v>46274</v>
       </c>
@@ -21699,8 +21922,11 @@
       <c r="J139" s="1">
         <v>199</v>
       </c>
-    </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K139" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A140" s="2">
         <v>46274</v>
       </c>
@@ -21722,8 +21948,11 @@
       <c r="J140" s="1">
         <v>50</v>
       </c>
-    </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K140" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="141" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A141" s="2">
         <v>46274</v>
       </c>
@@ -21751,8 +21980,11 @@
       <c r="J141" s="1">
         <v>199</v>
       </c>
-    </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K141" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A142" s="2">
         <v>46274</v>
       </c>
@@ -21774,8 +22006,11 @@
       <c r="J142" s="1">
         <v>50</v>
       </c>
-    </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K142" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A143" s="2">
         <v>46274</v>
       </c>
@@ -21803,8 +22038,11 @@
       <c r="J143" s="1">
         <v>199</v>
       </c>
-    </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K143" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A144" s="2">
         <v>46274</v>
       </c>
@@ -21825,6 +22063,9 @@
       </c>
       <c r="J144" s="1">
         <v>70</v>
+      </c>
+      <c r="K144" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.3">
@@ -21855,6 +22096,9 @@
       <c r="J145" s="1">
         <v>299</v>
       </c>
+      <c r="K145" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A146" s="2">
@@ -21884,6 +22128,9 @@
       <c r="J146" s="1">
         <v>299</v>
       </c>
+      <c r="K146" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A147" s="2">
@@ -21907,6 +22154,9 @@
       <c r="J147" s="1">
         <v>50</v>
       </c>
+      <c r="K147" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="148" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A148" s="2">
@@ -21936,6 +22186,9 @@
       <c r="J148" s="1">
         <v>199</v>
       </c>
+      <c r="K148" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A149" s="2">
@@ -22011,6 +22264,9 @@
       <c r="J151" s="1">
         <v>50</v>
       </c>
+      <c r="K151" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="152" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A152" s="2">
@@ -22040,6 +22296,9 @@
       <c r="J152" s="1">
         <v>99</v>
       </c>
+      <c r="K152" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="153" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A153" s="2">
@@ -22063,6 +22322,9 @@
       <c r="J153" s="1">
         <v>50</v>
       </c>
+      <c r="K153" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="154" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A154" s="2">
@@ -22089,6 +22351,9 @@
       <c r="J154" s="1">
         <v>599</v>
       </c>
+      <c r="K154" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="155" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A155" s="2">
@@ -22164,6 +22429,9 @@
       <c r="J157" s="1">
         <v>50</v>
       </c>
+      <c r="K157" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="158" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A158" s="2">
@@ -22193,6 +22461,9 @@
       <c r="J158" s="1">
         <v>199</v>
       </c>
+      <c r="K158" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="159" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A159" s="2">
@@ -22216,6 +22487,9 @@
       <c r="J159" s="1">
         <v>50</v>
       </c>
+      <c r="K159" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="160" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A160" s="2">
@@ -22239,8 +22513,11 @@
       <c r="J160" s="1">
         <v>70</v>
       </c>
-    </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K160" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="161" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A161" s="2">
         <v>46295</v>
       </c>
@@ -22262,8 +22539,11 @@
       <c r="J161" s="1">
         <v>50</v>
       </c>
-    </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K161" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="162" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A162" s="2">
         <v>46295</v>
       </c>
@@ -22291,8 +22571,11 @@
       <c r="J162" s="1">
         <v>99</v>
       </c>
-    </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K162" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="163" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A163" s="2">
         <v>46295</v>
       </c>
@@ -22314,8 +22597,11 @@
       <c r="J163" s="1">
         <v>70</v>
       </c>
-    </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K163" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="164" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A164" s="2">
         <v>46295</v>
       </c>
@@ -22337,8 +22623,11 @@
       <c r="J164" s="1">
         <v>70</v>
       </c>
-    </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K164" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="165" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A165" s="2">
         <v>46295</v>
       </c>
@@ -22360,8 +22649,11 @@
       <c r="J165" s="1">
         <v>50</v>
       </c>
-    </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K165" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="166" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A166" s="2">
         <v>46295</v>
       </c>
@@ -22389,8 +22681,11 @@
       <c r="J166" s="1">
         <v>99</v>
       </c>
-    </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K166" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="167" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A167" s="2">
         <v>46297</v>
       </c>
@@ -22412,8 +22707,11 @@
       <c r="J167" s="1">
         <v>50</v>
       </c>
-    </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K167" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="168" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A168" s="2">
         <v>46297</v>
       </c>
@@ -22441,8 +22739,11 @@
       <c r="J168" s="1">
         <v>229</v>
       </c>
-    </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K168" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="169" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A169" s="2">
         <v>46297</v>
       </c>
@@ -22464,8 +22765,11 @@
       <c r="J169" s="1">
         <v>50</v>
       </c>
-    </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K169" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="170" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A170" s="2">
         <v>46297</v>
       </c>
@@ -22493,8 +22797,11 @@
       <c r="J170" s="1">
         <v>229</v>
       </c>
-    </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K170" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="171" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A171" s="2">
         <v>46297</v>
       </c>
@@ -22525,8 +22832,11 @@
       <c r="J171" s="1">
         <v>319</v>
       </c>
-    </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K171" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="172" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A172" s="2">
         <v>46297</v>
       </c>
@@ -22548,8 +22858,11 @@
       <c r="J172" s="1">
         <v>50</v>
       </c>
-    </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K172" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="173" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A173" s="2">
         <v>46297</v>
       </c>
@@ -22577,8 +22890,11 @@
       <c r="J173" s="1">
         <v>749</v>
       </c>
-    </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K173" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="174" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A174" s="2">
         <v>46304</v>
       </c>
@@ -22600,8 +22916,11 @@
       <c r="J174" s="1">
         <v>70</v>
       </c>
-    </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K174" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="175" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A175" s="2">
         <v>46304</v>
       </c>
@@ -22629,8 +22948,11 @@
       <c r="J175" s="1">
         <v>109</v>
       </c>
-    </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K175" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="176" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A176" s="2">
         <v>46304</v>
       </c>
@@ -22652,8 +22974,11 @@
       <c r="J176" s="1">
         <v>70</v>
       </c>
-    </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K176" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="177" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A177" s="2">
         <v>46304</v>
       </c>
@@ -22680,6 +23005,9 @@
       </c>
       <c r="J177" s="1">
         <v>109</v>
+      </c>
+      <c r="K177" t="s">
+        <v>126</v>
       </c>
     </row>
   </sheetData>

--- a/B2B CAMPAÑAS.xlsx
+++ b/B2B CAMPAÑAS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EMANUEL.CONTRERAS\Desktop\B2B Y PRECISA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\Actualización Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B61CECE0-54BD-40EE-AB9E-6B954044E4FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49E3987A-A6D5-430E-A240-FEA716BB2753}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{7747799D-4BD1-4446-9F7D-9AFFD1051C34}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7747799D-4BD1-4446-9F7D-9AFFD1051C34}"/>
   </bookViews>
   <sheets>
     <sheet name="REGISTRO" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3821" uniqueCount="1017">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3921" uniqueCount="1038">
   <si>
     <t>DNI</t>
   </si>
@@ -3080,21 +3080,106 @@
   </si>
   <si>
     <t>MO.BAS.MUJ.AT.MCW013</t>
+  </si>
+  <si>
+    <t>45444050</t>
+  </si>
+  <si>
+    <t>Miranda Huaman Pablo Humberto</t>
+  </si>
+  <si>
+    <t>Coronel Singuña Miguel Angel</t>
+  </si>
+  <si>
+    <t>Vela Gamero Mary Angela Daniela</t>
+  </si>
+  <si>
+    <t>Aquino Navarro Lourdes Fabiola</t>
+  </si>
+  <si>
+    <t>Hidalgo Ruiz Rosa Teresa</t>
+  </si>
+  <si>
+    <t>Palacin Vega Alcida Yovana</t>
+  </si>
+  <si>
+    <t>Arce Monge Elizabeth</t>
+  </si>
+  <si>
+    <t>Diaz Ochavano Lucia Alexandra</t>
+  </si>
+  <si>
+    <t>40047150</t>
+  </si>
+  <si>
+    <t>Oncebay Buleje Julia Antonia</t>
+  </si>
+  <si>
+    <t>Garcia Murillo Florinda Claudia</t>
+  </si>
+  <si>
+    <t>Rios Moreno Kassy Vanessa</t>
+  </si>
+  <si>
+    <t>Orellana Bastidas Reysheel Alexia</t>
+  </si>
+  <si>
+    <t>Brisuela Asencio Alejandro</t>
+  </si>
+  <si>
+    <t>Reupo Fernandez Anita Isabel</t>
+  </si>
+  <si>
+    <t>Culis Romero Zarai Rosario</t>
+  </si>
+  <si>
+    <t>Guzman Flores Giomar Ruben</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El Agustino </t>
+  </si>
+  <si>
+    <t>ATENTO</t>
+  </si>
+  <si>
+    <t>MO.BAS.HO.AT.MKEV150</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="&quot;S/&quot;\ #,##0.00"/>
+    <numFmt numFmtId="167" formatCode="_-&quot;S/&quot;\ * #,##0.00_-;\-&quot;S/&quot;\ * #,##0.00_-;_-&quot;S/&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -3115,16 +3200,39 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="6" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="9">
+    <cellStyle name="Hipervínculo 2" xfId="4" xr:uid="{CC19D78D-5404-41FC-B243-F36C3B59B8A5}"/>
+    <cellStyle name="Hyperlink" xfId="5" xr:uid="{B56C74E7-D8C5-4079-8D3A-28B0195AD674}"/>
+    <cellStyle name="Moneda 2" xfId="6" xr:uid="{9EBE7099-EACE-4F89-80CB-962821B8D824}"/>
+    <cellStyle name="Moneda 3" xfId="8" xr:uid="{D38D5466-9F57-49FC-8A07-B1AB76A82E84}"/>
+    <cellStyle name="Moneda 4" xfId="1" xr:uid="{B1B3121D-DC2A-4141-9827-60D87288401C}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="3" xr:uid="{80839579-EA55-456B-8058-D6FD8D0D3AE4}"/>
+    <cellStyle name="Normal 3" xfId="2" xr:uid="{24A5F5F4-7AB7-48FF-9FC3-9B41CA8EB5DD}"/>
+    <cellStyle name="Normal 4" xfId="7" xr:uid="{AC437859-20CB-4732-919C-95FD87A41F96}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3140,9 +3248,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3180,7 +3288,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -3286,7 +3394,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3428,7 +3536,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3436,7 +3544,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F72DAC60-1610-420C-8C80-CD65C2690876}">
-  <dimension ref="A1:J464"/>
+  <dimension ref="A1:J480"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" style="2" bestFit="1" customWidth="1"/>
@@ -17940,6 +18048,518 @@
         <v>931217628</v>
       </c>
     </row>
+    <row r="465" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A465" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B465" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C465" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D465">
+        <v>45444050</v>
+      </c>
+      <c r="E465" t="s">
+        <v>1018</v>
+      </c>
+      <c r="F465" s="2">
+        <v>32472</v>
+      </c>
+      <c r="G465">
+        <v>37</v>
+      </c>
+      <c r="H465" t="s">
+        <v>1035</v>
+      </c>
+      <c r="I465" t="s">
+        <v>17</v>
+      </c>
+      <c r="J465">
+        <v>972709238</v>
+      </c>
+    </row>
+    <row r="466" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A466" s="4">
+        <v>46315</v>
+      </c>
+      <c r="B466" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C466" s="3" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D466">
+        <v>44531029</v>
+      </c>
+      <c r="E466" t="s">
+        <v>1019</v>
+      </c>
+      <c r="F466" s="2">
+        <v>32009</v>
+      </c>
+      <c r="G466">
+        <v>39</v>
+      </c>
+      <c r="H466" t="s">
+        <v>962</v>
+      </c>
+      <c r="I466" t="s">
+        <v>17</v>
+      </c>
+      <c r="J466">
+        <v>950305910</v>
+      </c>
+    </row>
+    <row r="467" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A467" s="4">
+        <v>46315</v>
+      </c>
+      <c r="B467" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C467" s="3" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D467">
+        <v>41596393</v>
+      </c>
+      <c r="E467" t="s">
+        <v>1020</v>
+      </c>
+      <c r="F467" s="2">
+        <v>30011</v>
+      </c>
+      <c r="G467">
+        <v>44</v>
+      </c>
+      <c r="H467" t="s">
+        <v>1035</v>
+      </c>
+      <c r="I467" t="s">
+        <v>17</v>
+      </c>
+      <c r="J467">
+        <v>983722397</v>
+      </c>
+    </row>
+    <row r="468" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A468" s="4">
+        <v>46315</v>
+      </c>
+      <c r="B468" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C468" s="3" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D468">
+        <v>71880373</v>
+      </c>
+      <c r="E468" t="s">
+        <v>1021</v>
+      </c>
+      <c r="F468" s="2">
+        <v>33904</v>
+      </c>
+      <c r="G468">
+        <v>33</v>
+      </c>
+      <c r="H468" t="s">
+        <v>102</v>
+      </c>
+      <c r="I468" t="s">
+        <v>9</v>
+      </c>
+      <c r="J468">
+        <v>949844314</v>
+      </c>
+    </row>
+    <row r="469" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A469" s="4">
+        <v>46315</v>
+      </c>
+      <c r="B469" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C469" s="3" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D469">
+        <v>10833705</v>
+      </c>
+      <c r="E469" t="s">
+        <v>1022</v>
+      </c>
+      <c r="F469" s="2">
+        <v>25003</v>
+      </c>
+      <c r="G469">
+        <v>58</v>
+      </c>
+      <c r="H469" t="s">
+        <v>38</v>
+      </c>
+      <c r="I469" t="s">
+        <v>9</v>
+      </c>
+      <c r="J469">
+        <v>989037259</v>
+      </c>
+    </row>
+    <row r="470" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A470" s="4">
+        <v>46315</v>
+      </c>
+      <c r="B470" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C470" s="3" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D470">
+        <v>10150151</v>
+      </c>
+      <c r="E470" t="s">
+        <v>1023</v>
+      </c>
+      <c r="F470" s="2">
+        <v>27441</v>
+      </c>
+      <c r="G470">
+        <v>51</v>
+      </c>
+      <c r="H470" t="s">
+        <v>256</v>
+      </c>
+      <c r="I470" t="s">
+        <v>9</v>
+      </c>
+      <c r="J470">
+        <v>927626508</v>
+      </c>
+    </row>
+    <row r="471" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A471" s="4">
+        <v>46315</v>
+      </c>
+      <c r="B471" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C471" s="3" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D471">
+        <v>41041142</v>
+      </c>
+      <c r="E471" t="s">
+        <v>1024</v>
+      </c>
+      <c r="F471" s="2">
+        <v>29811</v>
+      </c>
+      <c r="G471">
+        <v>45</v>
+      </c>
+      <c r="H471" t="s">
+        <v>45</v>
+      </c>
+      <c r="I471" t="s">
+        <v>9</v>
+      </c>
+      <c r="J471">
+        <v>915153511</v>
+      </c>
+    </row>
+    <row r="472" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A472" s="4">
+        <v>46315</v>
+      </c>
+      <c r="B472" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C472" s="3" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D472">
+        <v>76071371</v>
+      </c>
+      <c r="E472" t="s">
+        <v>1025</v>
+      </c>
+      <c r="F472" s="2">
+        <v>38128</v>
+      </c>
+      <c r="G472">
+        <v>22</v>
+      </c>
+      <c r="H472" t="s">
+        <v>16</v>
+      </c>
+      <c r="I472" t="s">
+        <v>9</v>
+      </c>
+      <c r="J472">
+        <v>930110847</v>
+      </c>
+    </row>
+    <row r="473" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A473" s="4">
+        <v>46315</v>
+      </c>
+      <c r="B473" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C473" s="3" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D473">
+        <v>40047150</v>
+      </c>
+      <c r="E473" t="s">
+        <v>1027</v>
+      </c>
+      <c r="F473" s="2">
+        <v>28852</v>
+      </c>
+      <c r="G473">
+        <v>47</v>
+      </c>
+      <c r="H473" t="s">
+        <v>45</v>
+      </c>
+      <c r="I473" t="s">
+        <v>9</v>
+      </c>
+      <c r="J473">
+        <v>997550115</v>
+      </c>
+    </row>
+    <row r="474" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A474" s="4">
+        <v>46315</v>
+      </c>
+      <c r="B474" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C474" s="3" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D474">
+        <v>43588639</v>
+      </c>
+      <c r="E474" t="s">
+        <v>1028</v>
+      </c>
+      <c r="F474" s="2">
+        <v>31434</v>
+      </c>
+      <c r="G474">
+        <v>40</v>
+      </c>
+      <c r="H474" t="s">
+        <v>13</v>
+      </c>
+      <c r="I474" t="s">
+        <v>9</v>
+      </c>
+      <c r="J474">
+        <v>903307682</v>
+      </c>
+    </row>
+    <row r="475" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A475" s="4">
+        <v>46315</v>
+      </c>
+      <c r="B475" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C475" s="3" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D475">
+        <v>48065836</v>
+      </c>
+      <c r="E475" t="s">
+        <v>1029</v>
+      </c>
+      <c r="F475" s="2">
+        <v>34150</v>
+      </c>
+      <c r="G475">
+        <v>33</v>
+      </c>
+      <c r="H475" t="s">
+        <v>102</v>
+      </c>
+      <c r="I475" t="s">
+        <v>9</v>
+      </c>
+      <c r="J475">
+        <v>954393531</v>
+      </c>
+    </row>
+    <row r="476" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A476" s="4">
+        <v>46315</v>
+      </c>
+      <c r="B476" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C476" s="3" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D476">
+        <v>74874601</v>
+      </c>
+      <c r="E476" t="s">
+        <v>1030</v>
+      </c>
+      <c r="F476" s="2">
+        <v>37160</v>
+      </c>
+      <c r="G476">
+        <v>25</v>
+      </c>
+      <c r="H476" t="s">
+        <v>45</v>
+      </c>
+      <c r="I476" t="s">
+        <v>9</v>
+      </c>
+      <c r="J476">
+        <v>920686868</v>
+      </c>
+    </row>
+    <row r="477" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A477" s="4">
+        <v>46315</v>
+      </c>
+      <c r="B477" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C477" s="3" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D477">
+        <v>73256110</v>
+      </c>
+      <c r="E477" t="s">
+        <v>1031</v>
+      </c>
+      <c r="F477" s="2">
+        <v>38144</v>
+      </c>
+      <c r="G477">
+        <v>22</v>
+      </c>
+      <c r="H477" t="s">
+        <v>30</v>
+      </c>
+      <c r="I477" t="s">
+        <v>17</v>
+      </c>
+      <c r="J477">
+        <v>953026803</v>
+      </c>
+    </row>
+    <row r="478" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A478" s="4">
+        <v>46315</v>
+      </c>
+      <c r="B478" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C478" s="3" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D478">
+        <v>45291894</v>
+      </c>
+      <c r="E478" t="s">
+        <v>1032</v>
+      </c>
+      <c r="F478" s="2">
+        <v>32397</v>
+      </c>
+      <c r="G478">
+        <v>38</v>
+      </c>
+      <c r="H478" t="s">
+        <v>953</v>
+      </c>
+      <c r="I478" t="s">
+        <v>9</v>
+      </c>
+      <c r="J478">
+        <v>951377692</v>
+      </c>
+    </row>
+    <row r="479" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A479" s="4">
+        <v>46315</v>
+      </c>
+      <c r="B479" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C479" s="3" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D479">
+        <v>73968251</v>
+      </c>
+      <c r="E479" t="s">
+        <v>1033</v>
+      </c>
+      <c r="F479" s="2">
+        <v>38044</v>
+      </c>
+      <c r="G479">
+        <v>22</v>
+      </c>
+      <c r="H479" t="s">
+        <v>45</v>
+      </c>
+      <c r="I479" t="s">
+        <v>9</v>
+      </c>
+      <c r="J479">
+        <v>903023906</v>
+      </c>
+    </row>
+    <row r="480" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A480" s="4">
+        <v>46315</v>
+      </c>
+      <c r="B480" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C480" s="3" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D480">
+        <v>46618433</v>
+      </c>
+      <c r="E480" t="s">
+        <v>1034</v>
+      </c>
+      <c r="F480" s="2">
+        <v>33181</v>
+      </c>
+      <c r="G480">
+        <v>35</v>
+      </c>
+      <c r="H480" t="s">
+        <v>45</v>
+      </c>
+      <c r="I480" t="s">
+        <v>17</v>
+      </c>
+      <c r="J480">
+        <v>921131844</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -17947,7 +18567,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E3A5197-674F-4EA2-AB94-B2E9CF4A156D}">
-  <dimension ref="A1:K177"/>
+  <dimension ref="A1:K180"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.5546875" style="2"/>
@@ -23010,6 +23630,97 @@
         <v>126</v>
       </c>
     </row>
+    <row r="178" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A178" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B178" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C178" s="6" t="s">
+        <v>1017</v>
+      </c>
+      <c r="D178" s="5" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E178" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="F178" s="7"/>
+      <c r="G178" s="7"/>
+      <c r="H178" s="7"/>
+      <c r="I178" s="7" t="s">
+        <v>1037</v>
+      </c>
+      <c r="J178" s="9">
+        <v>70</v>
+      </c>
+      <c r="K178" s="7" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="179" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A179" s="8">
+        <v>46315</v>
+      </c>
+      <c r="B179" s="7" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C179" s="6" t="s">
+        <v>1017</v>
+      </c>
+      <c r="D179" s="5" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E179" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="F179" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="G179" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="H179" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="I179" s="7"/>
+      <c r="J179" s="9">
+        <v>109</v>
+      </c>
+      <c r="K179" s="7" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="180" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A180" s="8">
+        <v>46315</v>
+      </c>
+      <c r="B180" s="7" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C180" s="6" t="s">
+        <v>1026</v>
+      </c>
+      <c r="D180" s="5" t="s">
+        <v>1027</v>
+      </c>
+      <c r="E180" s="7" t="s">
+        <v>964</v>
+      </c>
+      <c r="F180" s="7"/>
+      <c r="G180" s="7"/>
+      <c r="H180" s="7"/>
+      <c r="I180" s="7" t="s">
+        <v>968</v>
+      </c>
+      <c r="J180" s="9">
+        <v>55.15</v>
+      </c>
+      <c r="K180" s="7" t="s">
+        <v>158</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
